--- a/artfynd/A 35468-2025 artfynd.xlsx
+++ b/artfynd/A 35468-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -917,6 +917,3250 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128068254</v>
+      </c>
+      <c r="B4" t="n">
+        <v>95779</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Keddebo, Boh</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>313003</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6523980</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128068261</v>
+      </c>
+      <c r="B5" t="n">
+        <v>5197</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Keddebo, Boh</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>312948</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6523938</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128068257</v>
+      </c>
+      <c r="B6" t="n">
+        <v>96747</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2590</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Odontoschisma denudatum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Keddebo, Boh</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>312950</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6523975</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128068249</v>
+      </c>
+      <c r="B7" t="n">
+        <v>5197</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Keddebo, Boh</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>313032</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6523992</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128068244</v>
+      </c>
+      <c r="B8" t="n">
+        <v>96747</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>2590</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Odontoschisma denudatum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Keddebo, Boh</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>312854</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6524011</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128068262</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91352</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1205</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Stor aspticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Phellinus populicola</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Keddebo, Boh</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>312931</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6523925</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128068264</v>
+      </c>
+      <c r="B10" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Keddebo, Boh</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>312958</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6523784</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128068271</v>
+      </c>
+      <c r="B11" t="n">
+        <v>5197</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Keddebo, Boh</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>312874</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6523699</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128068239</v>
+      </c>
+      <c r="B12" t="n">
+        <v>95790</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Keddebo, Boh</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>312713</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6524182</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128068265</v>
+      </c>
+      <c r="B13" t="n">
+        <v>5197</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Keddebo, Boh</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>312958</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6523784</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128068242</v>
+      </c>
+      <c r="B14" t="n">
+        <v>92631</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Keddebo, Boh</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>312801</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6523989</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128068243</v>
+      </c>
+      <c r="B15" t="n">
+        <v>96747</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>2590</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Odontoschisma denudatum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Keddebo, Boh</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>312856</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6523899</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128068240</v>
+      </c>
+      <c r="B16" t="n">
+        <v>95584</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>2779</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Guldlockmossa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Homalothecium sericeum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Keddebo, Boh</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>312713</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6524182</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128068258</v>
+      </c>
+      <c r="B17" t="n">
+        <v>43942</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>101735</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Jättesvampmal</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Scardia boletella</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Keddebo, Boh</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>312958</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6523975</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128068250</v>
+      </c>
+      <c r="B18" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Keddebo, Boh</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>313032</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6523992</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128068263</v>
+      </c>
+      <c r="B19" t="n">
+        <v>96711</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>53</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Keddebo, Boh</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>312975</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6523853</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128068256</v>
+      </c>
+      <c r="B20" t="n">
+        <v>96711</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>53</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Keddebo, Boh</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>312927</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6523972</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128068272</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57663</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Keddebo, Boh</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>312856</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6523735</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128068251</v>
+      </c>
+      <c r="B22" t="n">
+        <v>96711</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>53</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Keddebo, Boh</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>313027</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6523988</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128068255</v>
+      </c>
+      <c r="B23" t="n">
+        <v>80086</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Keddebo, Boh</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>313003</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6523980</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128068266</v>
+      </c>
+      <c r="B24" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Keddebo, Boh</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>312948</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6523764</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>128068245</v>
+      </c>
+      <c r="B25" t="n">
+        <v>5197</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Keddebo, Boh</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>312898</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6524038</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>128068269</v>
+      </c>
+      <c r="B26" t="n">
+        <v>4779</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Keddebo, Boh</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>312859</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6523647</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>128068270</v>
+      </c>
+      <c r="B27" t="n">
+        <v>75085</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Keddebo, Boh</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>312865</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6523655</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>128068241</v>
+      </c>
+      <c r="B28" t="n">
+        <v>91361</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Keddebo, Boh</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>312717</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6524079</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>128068253</v>
+      </c>
+      <c r="B29" t="n">
+        <v>91325</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>4660</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Rävticka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Inocutis rheades</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Keddebo, Boh</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>313007</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6523966</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>128068248</v>
+      </c>
+      <c r="B30" t="n">
+        <v>91306</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Keddebo, Boh</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>313036</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6523992</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>128068238</v>
+      </c>
+      <c r="B31" t="n">
+        <v>56858</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Keddebo, Boh</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>312809</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6524225</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>128068252</v>
+      </c>
+      <c r="B32" t="n">
+        <v>75085</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Keddebo, Boh</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>313022</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6524003</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>128068260</v>
+      </c>
+      <c r="B33" t="n">
+        <v>91394</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>5321</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Barkticka</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Oxyporus corticola</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Fr.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Keddebo, Boh</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>312956</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6523961</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35468-2025 artfynd.xlsx
+++ b/artfynd/A 35468-2025 artfynd.xlsx
@@ -922,7 +922,7 @@
         <v>128068254</v>
       </c>
       <c r="B4" t="n">
-        <v>95779</v>
+        <v>95787</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128068261</v>
+        <v>128068257</v>
       </c>
       <c r="B5" t="n">
-        <v>5197</v>
+        <v>96755</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1042,39 +1042,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>105930</v>
+        <v>2590</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>312948</v>
+        <v>312950</v>
       </c>
       <c r="R5" t="n">
-        <v>6523938</v>
+        <v>6523975</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1117,21 +1112,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1148,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128068257</v>
+        <v>128068261</v>
       </c>
       <c r="B6" t="n">
-        <v>96747</v>
+        <v>5197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1159,34 +1139,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2590</v>
+        <v>105930</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>312950</v>
+        <v>312948</v>
       </c>
       <c r="R6" t="n">
-        <v>6523975</v>
+        <v>6523938</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1229,6 +1214,21 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1365,7 +1365,7 @@
         <v>128068244</v>
       </c>
       <c r="B8" t="n">
-        <v>96747</v>
+        <v>96755</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>128068262</v>
       </c>
       <c r="B9" t="n">
-        <v>91352</v>
+        <v>91360</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1810,10 +1810,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128068239</v>
+        <v>128068242</v>
       </c>
       <c r="B12" t="n">
-        <v>95790</v>
+        <v>92639</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1821,21 +1821,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2667</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>312713</v>
+        <v>312801</v>
       </c>
       <c r="R12" t="n">
-        <v>6524182</v>
+        <v>6523989</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128068265</v>
+        <v>128068239</v>
       </c>
       <c r="B13" t="n">
-        <v>5197</v>
+        <v>95798</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,39 +1918,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>105930</v>
+        <v>2667</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>312958</v>
+        <v>312713</v>
       </c>
       <c r="R13" t="n">
-        <v>6523784</v>
+        <v>6524182</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1993,21 +1988,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2024,10 +2004,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128068242</v>
+        <v>128068265</v>
       </c>
       <c r="B14" t="n">
-        <v>92631</v>
+        <v>5197</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2035,34 +2015,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>105930</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>312801</v>
+        <v>312958</v>
       </c>
       <c r="R14" t="n">
-        <v>6523989</v>
+        <v>6523784</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2105,6 +2090,21 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2124,7 +2124,7 @@
         <v>128068243</v>
       </c>
       <c r="B15" t="n">
-        <v>96747</v>
+        <v>96755</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>128068240</v>
       </c>
       <c r="B16" t="n">
-        <v>95584</v>
+        <v>95592</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>128068263</v>
       </c>
       <c r="B19" t="n">
-        <v>96711</v>
+        <v>96719</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         <v>128068256</v>
       </c>
       <c r="B20" t="n">
-        <v>96711</v>
+        <v>96719</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>128068272</v>
       </c>
       <c r="B21" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
         <v>128068251</v>
       </c>
       <c r="B22" t="n">
-        <v>96711</v>
+        <v>96719</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>128068255</v>
       </c>
       <c r="B23" t="n">
-        <v>80086</v>
+        <v>80092</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3043,10 +3043,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128068266</v>
+        <v>128068269</v>
       </c>
       <c r="B24" t="n">
-        <v>8450</v>
+        <v>4779</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3054,27 +3054,27 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>102306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3083,10 +3083,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>312948</v>
+        <v>312859</v>
       </c>
       <c r="R24" t="n">
-        <v>6523764</v>
+        <v>6523647</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3132,17 +3132,17 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3272,10 +3272,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128068269</v>
+        <v>128068266</v>
       </c>
       <c r="B26" t="n">
-        <v>4779</v>
+        <v>8450</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3283,27 +3283,27 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102306</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3312,10 +3312,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>312859</v>
+        <v>312948</v>
       </c>
       <c r="R26" t="n">
-        <v>6523647</v>
+        <v>6523764</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3361,17 +3361,17 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3392,7 +3392,7 @@
         <v>128068270</v>
       </c>
       <c r="B27" t="n">
-        <v>75085</v>
+        <v>75091</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3501,32 +3501,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128068241</v>
+        <v>128068248</v>
       </c>
       <c r="B28" t="n">
-        <v>91361</v>
+        <v>91314</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5442</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3536,10 +3536,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>312717</v>
+        <v>313036</v>
       </c>
       <c r="R28" t="n">
-        <v>6524079</v>
+        <v>6523992</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3585,17 +3585,17 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3613,32 +3613,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128068253</v>
+        <v>128068241</v>
       </c>
       <c r="B29" t="n">
-        <v>91325</v>
+        <v>91369</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4660</v>
+        <v>5442</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3648,10 +3648,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>313007</v>
+        <v>312717</v>
       </c>
       <c r="R29" t="n">
-        <v>6523966</v>
+        <v>6524079</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3697,17 +3697,17 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3725,10 +3725,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128068248</v>
+        <v>128068253</v>
       </c>
       <c r="B30" t="n">
-        <v>91306</v>
+        <v>91333</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3736,21 +3736,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>4660</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3760,10 +3760,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>313036</v>
+        <v>313007</v>
       </c>
       <c r="R30" t="n">
-        <v>6523992</v>
+        <v>6523966</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3809,17 +3809,17 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3840,7 +3840,7 @@
         <v>128068238</v>
       </c>
       <c r="B31" t="n">
-        <v>56858</v>
+        <v>56864</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3938,10 +3938,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128068252</v>
+        <v>128068260</v>
       </c>
       <c r="B32" t="n">
-        <v>75085</v>
+        <v>91402</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3949,21 +3949,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6426</v>
+        <v>5321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3973,10 +3973,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>313022</v>
+        <v>312956</v>
       </c>
       <c r="R32" t="n">
-        <v>6524003</v>
+        <v>6523961</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4017,22 +4017,23 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4050,10 +4051,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128068260</v>
+        <v>128068252</v>
       </c>
       <c r="B33" t="n">
-        <v>91394</v>
+        <v>75091</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4061,21 +4062,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5321</v>
+        <v>6426</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4085,10 +4086,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>312956</v>
+        <v>313022</v>
       </c>
       <c r="R33" t="n">
-        <v>6523961</v>
+        <v>6524003</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4129,23 +4130,22 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>

--- a/artfynd/A 35468-2025 artfynd.xlsx
+++ b/artfynd/A 35468-2025 artfynd.xlsx
@@ -922,7 +922,7 @@
         <v>128068254</v>
       </c>
       <c r="B4" t="n">
-        <v>95787</v>
+        <v>95788</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>128068257</v>
       </c>
       <c r="B5" t="n">
-        <v>96755</v>
+        <v>96756</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>128068244</v>
       </c>
       <c r="B8" t="n">
-        <v>96755</v>
+        <v>96756</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>128068262</v>
       </c>
       <c r="B9" t="n">
-        <v>91360</v>
+        <v>91361</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1810,10 +1810,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128068242</v>
+        <v>128068239</v>
       </c>
       <c r="B12" t="n">
-        <v>92639</v>
+        <v>95799</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1821,21 +1821,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>2667</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>312801</v>
+        <v>312713</v>
       </c>
       <c r="R12" t="n">
-        <v>6523989</v>
+        <v>6524182</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128068239</v>
+        <v>128068265</v>
       </c>
       <c r="B13" t="n">
-        <v>95798</v>
+        <v>5197</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,34 +1918,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2667</v>
+        <v>105930</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>312713</v>
+        <v>312958</v>
       </c>
       <c r="R13" t="n">
-        <v>6524182</v>
+        <v>6523784</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1988,6 +1993,21 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2004,10 +2024,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128068265</v>
+        <v>128068242</v>
       </c>
       <c r="B14" t="n">
-        <v>5197</v>
+        <v>92640</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2015,39 +2035,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>105930</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>312958</v>
+        <v>312801</v>
       </c>
       <c r="R14" t="n">
-        <v>6523784</v>
+        <v>6523989</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2090,21 +2105,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2124,7 +2124,7 @@
         <v>128068243</v>
       </c>
       <c r="B15" t="n">
-        <v>96755</v>
+        <v>96756</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>128068240</v>
       </c>
       <c r="B16" t="n">
-        <v>95592</v>
+        <v>95593</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2315,10 +2315,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128068258</v>
+        <v>128068250</v>
       </c>
       <c r="B17" t="n">
-        <v>43942</v>
+        <v>5177</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2326,39 +2326,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>101735</v>
+        <v>100526</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>312958</v>
+        <v>313032</v>
       </c>
       <c r="R17" t="n">
-        <v>6523975</v>
+        <v>6523992</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2399,9 +2399,23 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2418,10 +2432,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128068250</v>
+        <v>128068258</v>
       </c>
       <c r="B18" t="n">
-        <v>5177</v>
+        <v>43942</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2429,39 +2443,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100526</v>
+        <v>101735</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>313032</v>
+        <v>312958</v>
       </c>
       <c r="R18" t="n">
-        <v>6523992</v>
+        <v>6523975</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2502,23 +2516,9 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2535,10 +2535,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128068263</v>
+        <v>128068272</v>
       </c>
       <c r="B19" t="n">
-        <v>96719</v>
+        <v>57669</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2546,34 +2546,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>312975</v>
+        <v>312856</v>
       </c>
       <c r="R19" t="n">
-        <v>6523853</v>
+        <v>6523735</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2632,10 +2640,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128068256</v>
+        <v>128068263</v>
       </c>
       <c r="B20" t="n">
-        <v>96719</v>
+        <v>96720</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2667,10 +2675,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>312927</v>
+        <v>312975</v>
       </c>
       <c r="R20" t="n">
-        <v>6523972</v>
+        <v>6523853</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2729,10 +2737,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128068272</v>
+        <v>128068256</v>
       </c>
       <c r="B21" t="n">
-        <v>57669</v>
+        <v>96720</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2740,42 +2748,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>312856</v>
+        <v>312927</v>
       </c>
       <c r="R21" t="n">
-        <v>6523735</v>
+        <v>6523972</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2837,7 +2837,7 @@
         <v>128068251</v>
       </c>
       <c r="B22" t="n">
-        <v>96719</v>
+        <v>96720</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3160,10 +3160,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128068245</v>
+        <v>128068266</v>
       </c>
       <c r="B25" t="n">
-        <v>5197</v>
+        <v>8450</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3171,34 +3171,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>105930</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>312898</v>
+        <v>312948</v>
       </c>
       <c r="R25" t="n">
-        <v>6524038</v>
+        <v>6523764</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3244,17 +3249,17 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3272,10 +3277,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128068266</v>
+        <v>128068245</v>
       </c>
       <c r="B26" t="n">
-        <v>8450</v>
+        <v>5197</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3283,39 +3288,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>105930</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>312948</v>
+        <v>312898</v>
       </c>
       <c r="R26" t="n">
-        <v>6523764</v>
+        <v>6524038</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3361,17 +3361,17 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3501,10 +3501,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128068248</v>
+        <v>128068253</v>
       </c>
       <c r="B28" t="n">
-        <v>91314</v>
+        <v>91334</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3512,21 +3512,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>4660</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3536,10 +3536,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>313036</v>
+        <v>313007</v>
       </c>
       <c r="R28" t="n">
-        <v>6523992</v>
+        <v>6523966</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3585,17 +3585,17 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3613,45 +3613,49 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128068241</v>
+        <v>128068238</v>
       </c>
       <c r="B29" t="n">
-        <v>91369</v>
+        <v>56864</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5442</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>312717</v>
+        <v>312809</v>
       </c>
       <c r="R29" t="n">
-        <v>6524079</v>
+        <v>6524225</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3694,21 +3698,6 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3725,10 +3714,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128068253</v>
+        <v>128068248</v>
       </c>
       <c r="B30" t="n">
-        <v>91333</v>
+        <v>91315</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3736,21 +3725,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4660</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3760,10 +3749,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>313007</v>
+        <v>313036</v>
       </c>
       <c r="R30" t="n">
-        <v>6523966</v>
+        <v>6523992</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3809,17 +3798,17 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3837,49 +3826,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128068238</v>
+        <v>128068241</v>
       </c>
       <c r="B31" t="n">
-        <v>56864</v>
+        <v>91370</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>312809</v>
+        <v>312717</v>
       </c>
       <c r="R31" t="n">
-        <v>6524225</v>
+        <v>6524079</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3922,6 +3907,21 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -3941,7 +3941,7 @@
         <v>128068260</v>
       </c>
       <c r="B32" t="n">
-        <v>91402</v>
+        <v>91403</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 35468-2025 artfynd.xlsx
+++ b/artfynd/A 35468-2025 artfynd.xlsx
@@ -1031,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128068257</v>
+        <v>128068261</v>
       </c>
       <c r="B5" t="n">
-        <v>96756</v>
+        <v>5197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1042,34 +1042,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2590</v>
+        <v>105930</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>312950</v>
+        <v>312948</v>
       </c>
       <c r="R5" t="n">
-        <v>6523975</v>
+        <v>6523938</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1112,6 +1117,21 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1128,10 +1148,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128068261</v>
+        <v>128068257</v>
       </c>
       <c r="B6" t="n">
-        <v>5197</v>
+        <v>96756</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,39 +1159,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>105930</v>
+        <v>2590</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>312948</v>
+        <v>312950</v>
       </c>
       <c r="R6" t="n">
-        <v>6523938</v>
+        <v>6523975</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1214,21 +1229,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1907,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128068265</v>
+        <v>128068242</v>
       </c>
       <c r="B13" t="n">
-        <v>5197</v>
+        <v>92640</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,39 +1918,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>105930</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>312958</v>
+        <v>312801</v>
       </c>
       <c r="R13" t="n">
-        <v>6523784</v>
+        <v>6523989</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1993,21 +1988,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2024,10 +2004,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128068242</v>
+        <v>128068265</v>
       </c>
       <c r="B14" t="n">
-        <v>92640</v>
+        <v>5197</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2035,34 +2015,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>105930</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>312801</v>
+        <v>312958</v>
       </c>
       <c r="R14" t="n">
-        <v>6523989</v>
+        <v>6523784</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2105,6 +2090,21 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2315,10 +2315,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128068250</v>
+        <v>128068258</v>
       </c>
       <c r="B17" t="n">
-        <v>5177</v>
+        <v>43942</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2326,39 +2326,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100526</v>
+        <v>101735</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>313032</v>
+        <v>312958</v>
       </c>
       <c r="R17" t="n">
-        <v>6523992</v>
+        <v>6523975</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2399,23 +2399,9 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2432,10 +2418,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128068258</v>
+        <v>128068250</v>
       </c>
       <c r="B18" t="n">
-        <v>43942</v>
+        <v>5177</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2443,39 +2429,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>101735</v>
+        <v>100526</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>312958</v>
+        <v>313032</v>
       </c>
       <c r="R18" t="n">
-        <v>6523975</v>
+        <v>6523992</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2516,9 +2502,23 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2535,10 +2535,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128068272</v>
+        <v>128068263</v>
       </c>
       <c r="B19" t="n">
-        <v>57669</v>
+        <v>96720</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2546,42 +2546,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>312856</v>
+        <v>312975</v>
       </c>
       <c r="R19" t="n">
-        <v>6523735</v>
+        <v>6523853</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2640,7 +2632,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128068263</v>
+        <v>128068256</v>
       </c>
       <c r="B20" t="n">
         <v>96720</v>
@@ -2675,10 +2667,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>312975</v>
+        <v>312927</v>
       </c>
       <c r="R20" t="n">
-        <v>6523853</v>
+        <v>6523972</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2737,10 +2729,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128068256</v>
+        <v>128068272</v>
       </c>
       <c r="B21" t="n">
-        <v>96720</v>
+        <v>57669</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2748,34 +2740,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>312927</v>
+        <v>312856</v>
       </c>
       <c r="R21" t="n">
-        <v>6523972</v>
+        <v>6523735</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2834,32 +2834,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128068251</v>
+        <v>128068255</v>
       </c>
       <c r="B22" t="n">
-        <v>96720</v>
+        <v>80092</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>229497</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2869,10 +2869,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>313027</v>
+        <v>313003</v>
       </c>
       <c r="R22" t="n">
-        <v>6523988</v>
+        <v>6523980</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2915,6 +2915,21 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -2931,32 +2946,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128068255</v>
+        <v>128068251</v>
       </c>
       <c r="B23" t="n">
-        <v>80092</v>
+        <v>96720</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229497</v>
+        <v>53</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2966,10 +2981,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>313003</v>
+        <v>313027</v>
       </c>
       <c r="R23" t="n">
-        <v>6523980</v>
+        <v>6523988</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3012,21 +3027,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3160,10 +3160,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128068266</v>
+        <v>128068245</v>
       </c>
       <c r="B25" t="n">
-        <v>8450</v>
+        <v>5197</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3171,39 +3171,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>105930</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>312948</v>
+        <v>312898</v>
       </c>
       <c r="R25" t="n">
-        <v>6523764</v>
+        <v>6524038</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3249,17 +3244,17 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3277,10 +3272,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128068245</v>
+        <v>128068266</v>
       </c>
       <c r="B26" t="n">
-        <v>5197</v>
+        <v>8450</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3288,34 +3283,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>105930</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>312898</v>
+        <v>312948</v>
       </c>
       <c r="R26" t="n">
-        <v>6524038</v>
+        <v>6523764</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3361,17 +3361,17 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3501,10 +3501,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128068253</v>
+        <v>128068238</v>
       </c>
       <c r="B28" t="n">
-        <v>91334</v>
+        <v>56864</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3512,34 +3512,38 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4660</v>
+        <v>100138</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>313007</v>
+        <v>312809</v>
       </c>
       <c r="R28" t="n">
-        <v>6523966</v>
+        <v>6524225</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3582,21 +3586,6 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3613,10 +3602,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128068238</v>
+        <v>128068248</v>
       </c>
       <c r="B29" t="n">
-        <v>56864</v>
+        <v>91315</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3624,38 +3613,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>312809</v>
+        <v>313036</v>
       </c>
       <c r="R29" t="n">
-        <v>6524225</v>
+        <v>6523992</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3698,6 +3683,21 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3714,32 +3714,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128068248</v>
+        <v>128068241</v>
       </c>
       <c r="B30" t="n">
-        <v>91315</v>
+        <v>91370</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>5442</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3749,10 +3749,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>313036</v>
+        <v>312717</v>
       </c>
       <c r="R30" t="n">
-        <v>6523992</v>
+        <v>6524079</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3798,17 +3798,17 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3826,32 +3826,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128068241</v>
+        <v>128068253</v>
       </c>
       <c r="B31" t="n">
-        <v>91370</v>
+        <v>91334</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5442</v>
+        <v>4660</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3861,10 +3861,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>312717</v>
+        <v>313007</v>
       </c>
       <c r="R31" t="n">
-        <v>6524079</v>
+        <v>6523966</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3910,17 +3910,17 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>

--- a/artfynd/A 35468-2025 artfynd.xlsx
+++ b/artfynd/A 35468-2025 artfynd.xlsx
@@ -2834,32 +2834,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128068251</v>
+        <v>128068255</v>
       </c>
       <c r="B22" t="n">
-        <v>96722</v>
+        <v>80092</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>229497</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2869,10 +2869,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>313027</v>
+        <v>313003</v>
       </c>
       <c r="R22" t="n">
-        <v>6523988</v>
+        <v>6523980</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2915,6 +2915,21 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -2931,32 +2946,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128068255</v>
+        <v>128068251</v>
       </c>
       <c r="B23" t="n">
-        <v>80092</v>
+        <v>96722</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229497</v>
+        <v>53</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2966,10 +2981,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>313003</v>
+        <v>313027</v>
       </c>
       <c r="R23" t="n">
-        <v>6523980</v>
+        <v>6523988</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3012,21 +3027,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3938,10 +3938,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128068260</v>
+        <v>128068252</v>
       </c>
       <c r="B32" t="n">
-        <v>91405</v>
+        <v>75091</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3949,21 +3949,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5321</v>
+        <v>6426</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3973,10 +3973,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>312956</v>
+        <v>313022</v>
       </c>
       <c r="R32" t="n">
-        <v>6523961</v>
+        <v>6524003</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4017,23 +4017,22 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4051,10 +4050,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128068252</v>
+        <v>128068260</v>
       </c>
       <c r="B33" t="n">
-        <v>75091</v>
+        <v>91405</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4062,21 +4061,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6426</v>
+        <v>5321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4086,10 +4085,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>313022</v>
+        <v>312956</v>
       </c>
       <c r="R33" t="n">
-        <v>6524003</v>
+        <v>6523961</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4130,22 +4129,23 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>

--- a/artfynd/A 35468-2025 artfynd.xlsx
+++ b/artfynd/A 35468-2025 artfynd.xlsx
@@ -922,7 +922,7 @@
         <v>128068254</v>
       </c>
       <c r="B4" t="n">
-        <v>95790</v>
+        <v>95798</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>128068257</v>
       </c>
       <c r="B5" t="n">
-        <v>96758</v>
+        <v>96766</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>128068244</v>
       </c>
       <c r="B8" t="n">
-        <v>96758</v>
+        <v>96766</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>128068262</v>
       </c>
       <c r="B9" t="n">
-        <v>91363</v>
+        <v>91371</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1927,10 +1927,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128068242</v>
+        <v>128068239</v>
       </c>
       <c r="B13" t="n">
-        <v>92642</v>
+        <v>95809</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1938,21 +1938,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>2667</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1962,10 +1962,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>312801</v>
+        <v>312713</v>
       </c>
       <c r="R13" t="n">
-        <v>6523989</v>
+        <v>6524182</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2024,10 +2024,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128068239</v>
+        <v>128068242</v>
       </c>
       <c r="B14" t="n">
-        <v>95801</v>
+        <v>92650</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2035,21 +2035,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2667</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2059,10 +2059,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>312713</v>
+        <v>312801</v>
       </c>
       <c r="R14" t="n">
-        <v>6524182</v>
+        <v>6523989</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2124,7 +2124,7 @@
         <v>128068243</v>
       </c>
       <c r="B15" t="n">
-        <v>96758</v>
+        <v>96766</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>128068240</v>
       </c>
       <c r="B16" t="n">
-        <v>95595</v>
+        <v>95603</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2315,10 +2315,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128068250</v>
+        <v>128068258</v>
       </c>
       <c r="B17" t="n">
-        <v>5177</v>
+        <v>43942</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2326,39 +2326,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100526</v>
+        <v>101735</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>313032</v>
+        <v>312958</v>
       </c>
       <c r="R17" t="n">
-        <v>6523992</v>
+        <v>6523975</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2399,23 +2399,9 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2432,10 +2418,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128068258</v>
+        <v>128068250</v>
       </c>
       <c r="B18" t="n">
-        <v>43942</v>
+        <v>5177</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2443,39 +2429,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>101735</v>
+        <v>100526</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>312958</v>
+        <v>313032</v>
       </c>
       <c r="R18" t="n">
-        <v>6523975</v>
+        <v>6523992</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2516,9 +2502,23 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2538,7 +2538,7 @@
         <v>128068263</v>
       </c>
       <c r="B19" t="n">
-        <v>96722</v>
+        <v>96730</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         <v>128068256</v>
       </c>
       <c r="B20" t="n">
-        <v>96722</v>
+        <v>96730</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>128068272</v>
       </c>
       <c r="B21" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2834,32 +2834,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128068255</v>
+        <v>128068251</v>
       </c>
       <c r="B22" t="n">
-        <v>80092</v>
+        <v>96730</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229497</v>
+        <v>53</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2869,10 +2869,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>313003</v>
+        <v>313027</v>
       </c>
       <c r="R22" t="n">
-        <v>6523980</v>
+        <v>6523988</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2915,21 +2915,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -2946,32 +2931,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128068251</v>
+        <v>128068255</v>
       </c>
       <c r="B23" t="n">
-        <v>96722</v>
+        <v>80095</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>53</v>
+        <v>229497</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2981,10 +2966,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>313027</v>
+        <v>313003</v>
       </c>
       <c r="R23" t="n">
-        <v>6523988</v>
+        <v>6523980</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3027,6 +3012,21 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3392,7 +3392,7 @@
         <v>128068270</v>
       </c>
       <c r="B27" t="n">
-        <v>75091</v>
+        <v>75094</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3501,10 +3501,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128068238</v>
+        <v>128068253</v>
       </c>
       <c r="B28" t="n">
-        <v>56864</v>
+        <v>91344</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3512,38 +3512,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100138</v>
+        <v>4660</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>312809</v>
+        <v>313007</v>
       </c>
       <c r="R28" t="n">
-        <v>6524225</v>
+        <v>6523966</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3586,6 +3582,21 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3605,7 +3616,7 @@
         <v>128068248</v>
       </c>
       <c r="B29" t="n">
-        <v>91317</v>
+        <v>91325</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3717,7 +3728,7 @@
         <v>128068241</v>
       </c>
       <c r="B30" t="n">
-        <v>91372</v>
+        <v>91380</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3826,10 +3837,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128068253</v>
+        <v>128068238</v>
       </c>
       <c r="B31" t="n">
-        <v>91336</v>
+        <v>56864</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3837,34 +3848,38 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4660</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>313007</v>
+        <v>312809</v>
       </c>
       <c r="R31" t="n">
-        <v>6523966</v>
+        <v>6524225</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3907,21 +3922,6 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -3941,7 +3941,7 @@
         <v>128068252</v>
       </c>
       <c r="B32" t="n">
-        <v>75091</v>
+        <v>75094</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         <v>128068260</v>
       </c>
       <c r="B33" t="n">
-        <v>91405</v>
+        <v>91413</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 35468-2025 artfynd.xlsx
+++ b/artfynd/A 35468-2025 artfynd.xlsx
@@ -3613,10 +3613,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128068248</v>
+        <v>128068238</v>
       </c>
       <c r="B29" t="n">
-        <v>91325</v>
+        <v>56864</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3624,34 +3624,38 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>313036</v>
+        <v>312809</v>
       </c>
       <c r="R29" t="n">
-        <v>6523992</v>
+        <v>6524225</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3694,21 +3698,6 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3725,32 +3714,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128068241</v>
+        <v>128068248</v>
       </c>
       <c r="B30" t="n">
-        <v>91380</v>
+        <v>91325</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5442</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3760,10 +3749,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>312717</v>
+        <v>313036</v>
       </c>
       <c r="R30" t="n">
-        <v>6524079</v>
+        <v>6523992</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3809,17 +3798,17 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3837,49 +3826,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128068238</v>
+        <v>128068241</v>
       </c>
       <c r="B31" t="n">
-        <v>56864</v>
+        <v>91380</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>312809</v>
+        <v>312717</v>
       </c>
       <c r="R31" t="n">
-        <v>6524225</v>
+        <v>6524079</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3922,6 +3907,21 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">

--- a/artfynd/A 35468-2025 artfynd.xlsx
+++ b/artfynd/A 35468-2025 artfynd.xlsx
@@ -922,7 +922,7 @@
         <v>128068254</v>
       </c>
       <c r="B4" t="n">
-        <v>95798</v>
+        <v>95891</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128068257</v>
+        <v>128068261</v>
       </c>
       <c r="B5" t="n">
-        <v>96766</v>
+        <v>5197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1042,34 +1042,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2590</v>
+        <v>105930</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>312950</v>
+        <v>312948</v>
       </c>
       <c r="R5" t="n">
-        <v>6523975</v>
+        <v>6523938</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1112,6 +1117,21 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1128,10 +1148,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128068261</v>
+        <v>128068257</v>
       </c>
       <c r="B6" t="n">
-        <v>5197</v>
+        <v>96859</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,39 +1159,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>105930</v>
+        <v>2590</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>312948</v>
+        <v>312950</v>
       </c>
       <c r="R6" t="n">
-        <v>6523938</v>
+        <v>6523975</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1214,21 +1229,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1365,7 +1365,7 @@
         <v>128068244</v>
       </c>
       <c r="B8" t="n">
-        <v>96766</v>
+        <v>96859</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>128068262</v>
       </c>
       <c r="B9" t="n">
-        <v>91371</v>
+        <v>91463</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128068264</v>
+        <v>128068271</v>
       </c>
       <c r="B10" t="n">
-        <v>5177</v>
+        <v>5197</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1582,43 +1582,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>312958</v>
+        <v>312874</v>
       </c>
       <c r="R10" t="n">
-        <v>6523784</v>
+        <v>6523699</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1659,7 +1655,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1693,10 +1688,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128068271</v>
+        <v>128068264</v>
       </c>
       <c r="B11" t="n">
-        <v>5197</v>
+        <v>5177</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1704,39 +1699,43 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>312874</v>
+        <v>312958</v>
       </c>
       <c r="R11" t="n">
-        <v>6523699</v>
+        <v>6523784</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1777,6 +1776,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1810,10 +1810,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128068265</v>
+        <v>128068242</v>
       </c>
       <c r="B12" t="n">
-        <v>5197</v>
+        <v>92742</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1821,39 +1821,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>105930</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>312958</v>
+        <v>312801</v>
       </c>
       <c r="R12" t="n">
-        <v>6523784</v>
+        <v>6523989</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1896,21 +1891,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1930,7 +1910,7 @@
         <v>128068239</v>
       </c>
       <c r="B13" t="n">
-        <v>95809</v>
+        <v>95902</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2024,10 +2004,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128068242</v>
+        <v>128068265</v>
       </c>
       <c r="B14" t="n">
-        <v>92650</v>
+        <v>5197</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2035,34 +2015,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>105930</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>312801</v>
+        <v>312958</v>
       </c>
       <c r="R14" t="n">
-        <v>6523989</v>
+        <v>6523784</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2105,6 +2090,21 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2124,7 +2124,7 @@
         <v>128068243</v>
       </c>
       <c r="B15" t="n">
-        <v>96766</v>
+        <v>96859</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>128068240</v>
       </c>
       <c r="B16" t="n">
-        <v>95603</v>
+        <v>95696</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         <v>128068258</v>
       </c>
       <c r="B17" t="n">
-        <v>43942</v>
+        <v>43950</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>128068263</v>
       </c>
       <c r="B19" t="n">
-        <v>96730</v>
+        <v>96823</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         <v>128068256</v>
       </c>
       <c r="B20" t="n">
-        <v>96730</v>
+        <v>96823</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>128068272</v>
       </c>
       <c r="B21" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2834,32 +2834,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128068251</v>
+        <v>128068255</v>
       </c>
       <c r="B22" t="n">
-        <v>96730</v>
+        <v>80148</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>229497</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2869,10 +2869,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>313027</v>
+        <v>313003</v>
       </c>
       <c r="R22" t="n">
-        <v>6523988</v>
+        <v>6523980</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2915,6 +2915,21 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -2931,32 +2946,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128068255</v>
+        <v>128068251</v>
       </c>
       <c r="B23" t="n">
-        <v>80095</v>
+        <v>96823</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229497</v>
+        <v>53</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2966,10 +2981,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>313003</v>
+        <v>313027</v>
       </c>
       <c r="R23" t="n">
-        <v>6523980</v>
+        <v>6523988</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3012,21 +3027,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3043,10 +3043,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128068245</v>
+        <v>128068269</v>
       </c>
       <c r="B24" t="n">
-        <v>5197</v>
+        <v>4779</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3054,34 +3054,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>105930</v>
+        <v>102306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>312898</v>
+        <v>312859</v>
       </c>
       <c r="R24" t="n">
-        <v>6524038</v>
+        <v>6523647</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3155,10 +3160,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128068266</v>
+        <v>128068245</v>
       </c>
       <c r="B25" t="n">
-        <v>8450</v>
+        <v>5197</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3166,39 +3171,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>105930</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>312948</v>
+        <v>312898</v>
       </c>
       <c r="R25" t="n">
-        <v>6523764</v>
+        <v>6524038</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3244,17 +3244,17 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3272,10 +3272,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128068269</v>
+        <v>128068266</v>
       </c>
       <c r="B26" t="n">
-        <v>4779</v>
+        <v>8450</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3283,27 +3283,27 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102306</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3312,10 +3312,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>312859</v>
+        <v>312948</v>
       </c>
       <c r="R26" t="n">
-        <v>6523647</v>
+        <v>6523764</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3361,17 +3361,17 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3392,7 +3392,7 @@
         <v>128068270</v>
       </c>
       <c r="B27" t="n">
-        <v>75094</v>
+        <v>75109</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3504,7 +3504,7 @@
         <v>128068253</v>
       </c>
       <c r="B28" t="n">
-        <v>91344</v>
+        <v>91436</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3613,10 +3613,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128068238</v>
+        <v>128068248</v>
       </c>
       <c r="B29" t="n">
-        <v>56864</v>
+        <v>91417</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3624,38 +3624,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>312809</v>
+        <v>313036</v>
       </c>
       <c r="R29" t="n">
-        <v>6524225</v>
+        <v>6523992</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3698,6 +3694,21 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3714,32 +3725,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128068248</v>
+        <v>128068241</v>
       </c>
       <c r="B30" t="n">
-        <v>91325</v>
+        <v>91472</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>5442</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3749,10 +3760,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>313036</v>
+        <v>312717</v>
       </c>
       <c r="R30" t="n">
-        <v>6523992</v>
+        <v>6524079</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3798,17 +3809,17 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3826,45 +3837,49 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128068241</v>
+        <v>128068238</v>
       </c>
       <c r="B31" t="n">
-        <v>91380</v>
+        <v>56876</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5442</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>312717</v>
+        <v>312809</v>
       </c>
       <c r="R31" t="n">
-        <v>6524079</v>
+        <v>6524225</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3907,21 +3922,6 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -3938,10 +3938,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128068252</v>
+        <v>128068260</v>
       </c>
       <c r="B32" t="n">
-        <v>75094</v>
+        <v>91505</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3949,21 +3949,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6426</v>
+        <v>5321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3973,10 +3973,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>313022</v>
+        <v>312956</v>
       </c>
       <c r="R32" t="n">
-        <v>6524003</v>
+        <v>6523961</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4017,22 +4017,23 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4050,10 +4051,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128068260</v>
+        <v>128068252</v>
       </c>
       <c r="B33" t="n">
-        <v>91413</v>
+        <v>75109</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4061,21 +4062,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5321</v>
+        <v>6426</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4085,10 +4086,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>312956</v>
+        <v>313022</v>
       </c>
       <c r="R33" t="n">
-        <v>6523961</v>
+        <v>6524003</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4129,23 +4130,22 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>

--- a/artfynd/A 35468-2025 artfynd.xlsx
+++ b/artfynd/A 35468-2025 artfynd.xlsx
@@ -2315,10 +2315,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128068258</v>
+        <v>128068250</v>
       </c>
       <c r="B17" t="n">
-        <v>43950</v>
+        <v>5177</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2326,39 +2326,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>101735</v>
+        <v>100526</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>312958</v>
+        <v>313032</v>
       </c>
       <c r="R17" t="n">
-        <v>6523975</v>
+        <v>6523992</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2399,9 +2399,23 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2418,10 +2432,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128068250</v>
+        <v>128068258</v>
       </c>
       <c r="B18" t="n">
-        <v>5177</v>
+        <v>43950</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2429,39 +2443,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100526</v>
+        <v>101735</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>313032</v>
+        <v>312958</v>
       </c>
       <c r="R18" t="n">
-        <v>6523992</v>
+        <v>6523975</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2502,23 +2516,9 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2834,32 +2834,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128068255</v>
+        <v>128068251</v>
       </c>
       <c r="B22" t="n">
-        <v>80148</v>
+        <v>96823</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229497</v>
+        <v>53</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2869,10 +2869,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>313003</v>
+        <v>313027</v>
       </c>
       <c r="R22" t="n">
-        <v>6523980</v>
+        <v>6523988</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2915,21 +2915,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -2946,32 +2931,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128068251</v>
+        <v>128068255</v>
       </c>
       <c r="B23" t="n">
-        <v>96823</v>
+        <v>80148</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>53</v>
+        <v>229497</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2981,10 +2966,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>313027</v>
+        <v>313003</v>
       </c>
       <c r="R23" t="n">
-        <v>6523988</v>
+        <v>6523980</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3027,6 +3012,21 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3501,10 +3501,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128068253</v>
+        <v>128068238</v>
       </c>
       <c r="B28" t="n">
-        <v>91436</v>
+        <v>56876</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3512,34 +3512,38 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4660</v>
+        <v>100138</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>313007</v>
+        <v>312809</v>
       </c>
       <c r="R28" t="n">
-        <v>6523966</v>
+        <v>6524225</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3582,21 +3586,6 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3613,10 +3602,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128068248</v>
+        <v>128068253</v>
       </c>
       <c r="B29" t="n">
-        <v>91417</v>
+        <v>91436</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3624,21 +3613,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>4660</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3648,10 +3637,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>313036</v>
+        <v>313007</v>
       </c>
       <c r="R29" t="n">
-        <v>6523992</v>
+        <v>6523966</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3697,17 +3686,17 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3725,32 +3714,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128068241</v>
+        <v>128068248</v>
       </c>
       <c r="B30" t="n">
-        <v>91472</v>
+        <v>91417</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5442</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3760,10 +3749,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>312717</v>
+        <v>313036</v>
       </c>
       <c r="R30" t="n">
-        <v>6524079</v>
+        <v>6523992</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3809,17 +3798,17 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3837,49 +3826,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128068238</v>
+        <v>128068241</v>
       </c>
       <c r="B31" t="n">
-        <v>56876</v>
+        <v>91472</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>312809</v>
+        <v>312717</v>
       </c>
       <c r="R31" t="n">
-        <v>6524225</v>
+        <v>6524079</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3922,6 +3907,21 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -3938,10 +3938,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128068260</v>
+        <v>128068252</v>
       </c>
       <c r="B32" t="n">
-        <v>91505</v>
+        <v>75109</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3949,21 +3949,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5321</v>
+        <v>6426</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3973,10 +3973,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>312956</v>
+        <v>313022</v>
       </c>
       <c r="R32" t="n">
-        <v>6523961</v>
+        <v>6524003</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4017,23 +4017,22 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4051,10 +4050,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128068252</v>
+        <v>128068260</v>
       </c>
       <c r="B33" t="n">
-        <v>75109</v>
+        <v>91505</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4062,21 +4061,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6426</v>
+        <v>5321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4086,10 +4085,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>313022</v>
+        <v>312956</v>
       </c>
       <c r="R33" t="n">
-        <v>6524003</v>
+        <v>6523961</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4130,22 +4129,23 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>

--- a/artfynd/A 35468-2025 artfynd.xlsx
+++ b/artfynd/A 35468-2025 artfynd.xlsx
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128068271</v>
+        <v>128068264</v>
       </c>
       <c r="B10" t="n">
-        <v>5197</v>
+        <v>5177</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1582,39 +1582,43 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>312874</v>
+        <v>312958</v>
       </c>
       <c r="R10" t="n">
-        <v>6523699</v>
+        <v>6523784</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1655,6 +1659,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1688,10 +1693,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128068264</v>
+        <v>128068271</v>
       </c>
       <c r="B11" t="n">
-        <v>5177</v>
+        <v>5197</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1699,43 +1704,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>312958</v>
+        <v>312874</v>
       </c>
       <c r="R11" t="n">
-        <v>6523784</v>
+        <v>6523699</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1776,7 +1777,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1810,10 +1810,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128068242</v>
+        <v>128068239</v>
       </c>
       <c r="B12" t="n">
-        <v>92742</v>
+        <v>95902</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1821,21 +1821,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>2667</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>312801</v>
+        <v>312713</v>
       </c>
       <c r="R12" t="n">
-        <v>6523989</v>
+        <v>6524182</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128068239</v>
+        <v>128068242</v>
       </c>
       <c r="B13" t="n">
-        <v>95902</v>
+        <v>92742</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,21 +1918,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2667</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1942,10 +1942,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>312713</v>
+        <v>312801</v>
       </c>
       <c r="R13" t="n">
-        <v>6524182</v>
+        <v>6523989</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2315,10 +2315,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128068250</v>
+        <v>128068258</v>
       </c>
       <c r="B17" t="n">
-        <v>5177</v>
+        <v>43950</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2326,39 +2326,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100526</v>
+        <v>101735</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>313032</v>
+        <v>312958</v>
       </c>
       <c r="R17" t="n">
-        <v>6523992</v>
+        <v>6523975</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2399,23 +2399,9 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2432,10 +2418,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128068258</v>
+        <v>128068250</v>
       </c>
       <c r="B18" t="n">
-        <v>43950</v>
+        <v>5177</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2443,39 +2429,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>101735</v>
+        <v>100526</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>312958</v>
+        <v>313032</v>
       </c>
       <c r="R18" t="n">
-        <v>6523975</v>
+        <v>6523992</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2516,9 +2502,23 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2834,32 +2834,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128068251</v>
+        <v>128068255</v>
       </c>
       <c r="B22" t="n">
-        <v>96823</v>
+        <v>80148</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>229497</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2869,10 +2869,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>313027</v>
+        <v>313003</v>
       </c>
       <c r="R22" t="n">
-        <v>6523988</v>
+        <v>6523980</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2915,6 +2915,21 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -2931,32 +2946,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128068255</v>
+        <v>128068251</v>
       </c>
       <c r="B23" t="n">
-        <v>80148</v>
+        <v>96823</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229497</v>
+        <v>53</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2966,10 +2981,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>313003</v>
+        <v>313027</v>
       </c>
       <c r="R23" t="n">
-        <v>6523980</v>
+        <v>6523988</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3012,21 +3027,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3043,10 +3043,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128068269</v>
+        <v>128068266</v>
       </c>
       <c r="B24" t="n">
-        <v>4779</v>
+        <v>8450</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3054,27 +3054,27 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>102306</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3083,10 +3083,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>312859</v>
+        <v>312948</v>
       </c>
       <c r="R24" t="n">
-        <v>6523647</v>
+        <v>6523764</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3132,17 +3132,17 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3160,10 +3160,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128068245</v>
+        <v>128068269</v>
       </c>
       <c r="B25" t="n">
-        <v>5197</v>
+        <v>4779</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3171,34 +3171,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>105930</v>
+        <v>102306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>312898</v>
+        <v>312859</v>
       </c>
       <c r="R25" t="n">
-        <v>6524038</v>
+        <v>6523647</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3272,10 +3277,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128068266</v>
+        <v>128068245</v>
       </c>
       <c r="B26" t="n">
-        <v>8450</v>
+        <v>5197</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3283,39 +3288,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>105930</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>312948</v>
+        <v>312898</v>
       </c>
       <c r="R26" t="n">
-        <v>6523764</v>
+        <v>6524038</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3361,17 +3361,17 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3501,10 +3501,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128068238</v>
+        <v>128068248</v>
       </c>
       <c r="B28" t="n">
-        <v>56876</v>
+        <v>91417</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3512,38 +3512,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>312809</v>
+        <v>313036</v>
       </c>
       <c r="R28" t="n">
-        <v>6524225</v>
+        <v>6523992</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3586,6 +3582,21 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3602,32 +3613,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128068253</v>
+        <v>128068241</v>
       </c>
       <c r="B29" t="n">
-        <v>91436</v>
+        <v>91472</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4660</v>
+        <v>5442</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3637,10 +3648,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>313007</v>
+        <v>312717</v>
       </c>
       <c r="R29" t="n">
-        <v>6523966</v>
+        <v>6524079</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3686,17 +3697,17 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3714,10 +3725,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128068248</v>
+        <v>128068253</v>
       </c>
       <c r="B30" t="n">
-        <v>91417</v>
+        <v>91436</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3725,21 +3736,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>4660</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3749,10 +3760,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>313036</v>
+        <v>313007</v>
       </c>
       <c r="R30" t="n">
-        <v>6523992</v>
+        <v>6523966</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3798,17 +3809,17 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3826,45 +3837,49 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128068241</v>
+        <v>128068238</v>
       </c>
       <c r="B31" t="n">
-        <v>91472</v>
+        <v>56876</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5442</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>312717</v>
+        <v>312809</v>
       </c>
       <c r="R31" t="n">
-        <v>6524079</v>
+        <v>6524225</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3907,21 +3922,6 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -3938,10 +3938,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128068252</v>
+        <v>128068260</v>
       </c>
       <c r="B32" t="n">
-        <v>75109</v>
+        <v>91505</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3949,21 +3949,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6426</v>
+        <v>5321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3973,10 +3973,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>313022</v>
+        <v>312956</v>
       </c>
       <c r="R32" t="n">
-        <v>6524003</v>
+        <v>6523961</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4017,22 +4017,23 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4050,10 +4051,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128068260</v>
+        <v>128068252</v>
       </c>
       <c r="B33" t="n">
-        <v>91505</v>
+        <v>75109</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4061,21 +4062,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5321</v>
+        <v>6426</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4085,10 +4086,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>312956</v>
+        <v>313022</v>
       </c>
       <c r="R33" t="n">
-        <v>6523961</v>
+        <v>6524003</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4129,23 +4130,22 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>

--- a/artfynd/A 35468-2025 artfynd.xlsx
+++ b/artfynd/A 35468-2025 artfynd.xlsx
@@ -1031,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128068261</v>
+        <v>128068257</v>
       </c>
       <c r="B5" t="n">
-        <v>5197</v>
+        <v>96859</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1042,39 +1042,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>105930</v>
+        <v>2590</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>312948</v>
+        <v>312950</v>
       </c>
       <c r="R5" t="n">
-        <v>6523938</v>
+        <v>6523975</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1117,21 +1112,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1148,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128068257</v>
+        <v>128068261</v>
       </c>
       <c r="B6" t="n">
-        <v>96859</v>
+        <v>5197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1159,34 +1139,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2590</v>
+        <v>105930</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>312950</v>
+        <v>312948</v>
       </c>
       <c r="R6" t="n">
-        <v>6523975</v>
+        <v>6523938</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1229,6 +1214,21 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -2834,32 +2834,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128068255</v>
+        <v>128068251</v>
       </c>
       <c r="B22" t="n">
-        <v>80148</v>
+        <v>96823</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229497</v>
+        <v>53</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2869,10 +2869,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>313003</v>
+        <v>313027</v>
       </c>
       <c r="R22" t="n">
-        <v>6523980</v>
+        <v>6523988</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2915,21 +2915,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -2946,32 +2931,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128068251</v>
+        <v>128068255</v>
       </c>
       <c r="B23" t="n">
-        <v>96823</v>
+        <v>80148</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>53</v>
+        <v>229497</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2981,10 +2966,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>313027</v>
+        <v>313003</v>
       </c>
       <c r="R23" t="n">
-        <v>6523988</v>
+        <v>6523980</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3027,6 +3012,21 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">

--- a/artfynd/A 35468-2025 artfynd.xlsx
+++ b/artfynd/A 35468-2025 artfynd.xlsx
@@ -922,7 +922,7 @@
         <v>128068254</v>
       </c>
       <c r="B4" t="n">
-        <v>95891</v>
+        <v>95903</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>128068257</v>
       </c>
       <c r="B5" t="n">
-        <v>96859</v>
+        <v>96871</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>128068244</v>
       </c>
       <c r="B8" t="n">
-        <v>96859</v>
+        <v>96871</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>128068262</v>
       </c>
       <c r="B9" t="n">
-        <v>91463</v>
+        <v>91475</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1810,10 +1810,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128068239</v>
+        <v>128068242</v>
       </c>
       <c r="B12" t="n">
-        <v>95902</v>
+        <v>92754</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1821,21 +1821,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2667</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>312713</v>
+        <v>312801</v>
       </c>
       <c r="R12" t="n">
-        <v>6524182</v>
+        <v>6523989</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128068242</v>
+        <v>128068239</v>
       </c>
       <c r="B13" t="n">
-        <v>92742</v>
+        <v>95914</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,21 +1918,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>2667</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1942,10 +1942,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>312801</v>
+        <v>312713</v>
       </c>
       <c r="R13" t="n">
-        <v>6523989</v>
+        <v>6524182</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2124,7 +2124,7 @@
         <v>128068243</v>
       </c>
       <c r="B15" t="n">
-        <v>96859</v>
+        <v>96871</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>128068240</v>
       </c>
       <c r="B16" t="n">
-        <v>95696</v>
+        <v>95708</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         <v>128068258</v>
       </c>
       <c r="B17" t="n">
-        <v>43950</v>
+        <v>43952</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2535,10 +2535,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128068263</v>
+        <v>128068272</v>
       </c>
       <c r="B19" t="n">
-        <v>96823</v>
+        <v>57686</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2546,34 +2546,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>312975</v>
+        <v>312856</v>
       </c>
       <c r="R19" t="n">
-        <v>6523853</v>
+        <v>6523735</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2632,10 +2640,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128068256</v>
+        <v>128068263</v>
       </c>
       <c r="B20" t="n">
-        <v>96823</v>
+        <v>96835</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2667,10 +2675,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>312927</v>
+        <v>312975</v>
       </c>
       <c r="R20" t="n">
-        <v>6523972</v>
+        <v>6523853</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2729,10 +2737,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128068272</v>
+        <v>128068256</v>
       </c>
       <c r="B21" t="n">
-        <v>57682</v>
+        <v>96835</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2740,42 +2748,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>312856</v>
+        <v>312927</v>
       </c>
       <c r="R21" t="n">
-        <v>6523735</v>
+        <v>6523972</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2834,32 +2834,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128068251</v>
+        <v>128068255</v>
       </c>
       <c r="B22" t="n">
-        <v>96823</v>
+        <v>80152</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>229497</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2869,10 +2869,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>313027</v>
+        <v>313003</v>
       </c>
       <c r="R22" t="n">
-        <v>6523988</v>
+        <v>6523980</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2915,6 +2915,21 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -2931,32 +2946,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128068255</v>
+        <v>128068251</v>
       </c>
       <c r="B23" t="n">
-        <v>80148</v>
+        <v>96835</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229497</v>
+        <v>53</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2966,10 +2981,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>313003</v>
+        <v>313027</v>
       </c>
       <c r="R23" t="n">
-        <v>6523980</v>
+        <v>6523988</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3012,21 +3027,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3043,10 +3043,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128068266</v>
+        <v>128068269</v>
       </c>
       <c r="B24" t="n">
-        <v>8450</v>
+        <v>4779</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3054,27 +3054,27 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>102306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3083,10 +3083,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>312948</v>
+        <v>312859</v>
       </c>
       <c r="R24" t="n">
-        <v>6523764</v>
+        <v>6523647</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3132,17 +3132,17 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3160,10 +3160,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128068269</v>
+        <v>128068245</v>
       </c>
       <c r="B25" t="n">
-        <v>4779</v>
+        <v>5197</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3171,39 +3171,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>102306</v>
+        <v>105930</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>312859</v>
+        <v>312898</v>
       </c>
       <c r="R25" t="n">
-        <v>6523647</v>
+        <v>6524038</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3277,10 +3272,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128068245</v>
+        <v>128068266</v>
       </c>
       <c r="B26" t="n">
-        <v>5197</v>
+        <v>8450</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3288,34 +3283,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>105930</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>312898</v>
+        <v>312948</v>
       </c>
       <c r="R26" t="n">
-        <v>6524038</v>
+        <v>6523764</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3361,17 +3361,17 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3392,7 +3392,7 @@
         <v>128068270</v>
       </c>
       <c r="B27" t="n">
-        <v>75109</v>
+        <v>75113</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3501,10 +3501,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128068248</v>
+        <v>128068238</v>
       </c>
       <c r="B28" t="n">
-        <v>91417</v>
+        <v>56880</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3512,34 +3512,38 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>313036</v>
+        <v>312809</v>
       </c>
       <c r="R28" t="n">
-        <v>6523992</v>
+        <v>6524225</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3582,21 +3586,6 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3613,32 +3602,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128068241</v>
+        <v>128068248</v>
       </c>
       <c r="B29" t="n">
-        <v>91472</v>
+        <v>91429</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5442</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3648,10 +3637,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>312717</v>
+        <v>313036</v>
       </c>
       <c r="R29" t="n">
-        <v>6524079</v>
+        <v>6523992</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3697,17 +3686,17 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3725,32 +3714,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128068253</v>
+        <v>128068241</v>
       </c>
       <c r="B30" t="n">
-        <v>91436</v>
+        <v>91484</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4660</v>
+        <v>5442</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3760,10 +3749,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>313007</v>
+        <v>312717</v>
       </c>
       <c r="R30" t="n">
-        <v>6523966</v>
+        <v>6524079</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3809,17 +3798,17 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3837,10 +3826,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128068238</v>
+        <v>128068253</v>
       </c>
       <c r="B31" t="n">
-        <v>56876</v>
+        <v>91448</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3848,38 +3837,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100138</v>
+        <v>4660</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>312809</v>
+        <v>313007</v>
       </c>
       <c r="R31" t="n">
-        <v>6524225</v>
+        <v>6523966</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3922,6 +3907,21 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -3941,7 +3941,7 @@
         <v>128068260</v>
       </c>
       <c r="B32" t="n">
-        <v>91505</v>
+        <v>91517</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4054,7 +4054,7 @@
         <v>128068252</v>
       </c>
       <c r="B33" t="n">
-        <v>75109</v>
+        <v>75113</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 35468-2025 artfynd.xlsx
+++ b/artfynd/A 35468-2025 artfynd.xlsx
@@ -3043,10 +3043,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128068269</v>
+        <v>128068245</v>
       </c>
       <c r="B24" t="n">
-        <v>4779</v>
+        <v>5197</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3054,39 +3054,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>102306</v>
+        <v>105930</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>312859</v>
+        <v>312898</v>
       </c>
       <c r="R24" t="n">
-        <v>6523647</v>
+        <v>6524038</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3160,10 +3155,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128068245</v>
+        <v>128068266</v>
       </c>
       <c r="B25" t="n">
-        <v>5197</v>
+        <v>8450</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3171,34 +3166,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>105930</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>312898</v>
+        <v>312948</v>
       </c>
       <c r="R25" t="n">
-        <v>6524038</v>
+        <v>6523764</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3244,17 +3244,17 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3272,10 +3272,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128068266</v>
+        <v>128068269</v>
       </c>
       <c r="B26" t="n">
-        <v>8450</v>
+        <v>4779</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3283,27 +3283,27 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>102306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3312,10 +3312,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>312948</v>
+        <v>312859</v>
       </c>
       <c r="R26" t="n">
-        <v>6523764</v>
+        <v>6523647</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3361,17 +3361,17 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>

--- a/artfynd/A 35468-2025 artfynd.xlsx
+++ b/artfynd/A 35468-2025 artfynd.xlsx
@@ -2834,32 +2834,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128068255</v>
+        <v>128068251</v>
       </c>
       <c r="B22" t="n">
-        <v>80152</v>
+        <v>96835</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229497</v>
+        <v>53</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2869,10 +2869,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>313003</v>
+        <v>313027</v>
       </c>
       <c r="R22" t="n">
-        <v>6523980</v>
+        <v>6523988</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2915,21 +2915,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -2946,32 +2931,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128068251</v>
+        <v>128068255</v>
       </c>
       <c r="B23" t="n">
-        <v>96835</v>
+        <v>80152</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>53</v>
+        <v>229497</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2981,10 +2966,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>313027</v>
+        <v>313003</v>
       </c>
       <c r="R23" t="n">
-        <v>6523988</v>
+        <v>6523980</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3027,6 +3012,21 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">

--- a/artfynd/A 35468-2025 artfynd.xlsx
+++ b/artfynd/A 35468-2025 artfynd.xlsx
@@ -922,7 +922,7 @@
         <v>128068254</v>
       </c>
       <c r="B4" t="n">
-        <v>95903</v>
+        <v>95905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>128068257</v>
       </c>
       <c r="B5" t="n">
-        <v>96871</v>
+        <v>96873</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>128068244</v>
       </c>
       <c r="B8" t="n">
-        <v>96871</v>
+        <v>96873</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>128068262</v>
       </c>
       <c r="B9" t="n">
-        <v>91475</v>
+        <v>91477</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128068264</v>
+        <v>128068271</v>
       </c>
       <c r="B10" t="n">
-        <v>5177</v>
+        <v>5197</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1582,43 +1582,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>312958</v>
+        <v>312874</v>
       </c>
       <c r="R10" t="n">
-        <v>6523784</v>
+        <v>6523699</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1659,7 +1655,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1693,10 +1688,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128068271</v>
+        <v>128068264</v>
       </c>
       <c r="B11" t="n">
-        <v>5197</v>
+        <v>5177</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1704,39 +1699,43 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>312874</v>
+        <v>312958</v>
       </c>
       <c r="R11" t="n">
-        <v>6523699</v>
+        <v>6523784</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1777,6 +1776,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1810,10 +1810,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128068242</v>
+        <v>128068239</v>
       </c>
       <c r="B12" t="n">
-        <v>92754</v>
+        <v>95916</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1821,21 +1821,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>2667</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>312801</v>
+        <v>312713</v>
       </c>
       <c r="R12" t="n">
-        <v>6523989</v>
+        <v>6524182</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128068239</v>
+        <v>128068242</v>
       </c>
       <c r="B13" t="n">
-        <v>95914</v>
+        <v>92756</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,21 +1918,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2667</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1942,10 +1942,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>312713</v>
+        <v>312801</v>
       </c>
       <c r="R13" t="n">
-        <v>6524182</v>
+        <v>6523989</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2124,7 +2124,7 @@
         <v>128068243</v>
       </c>
       <c r="B15" t="n">
-        <v>96871</v>
+        <v>96873</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>128068240</v>
       </c>
       <c r="B16" t="n">
-        <v>95708</v>
+        <v>95710</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2535,10 +2535,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128068272</v>
+        <v>128068263</v>
       </c>
       <c r="B19" t="n">
-        <v>57686</v>
+        <v>96837</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2546,42 +2546,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>312856</v>
+        <v>312975</v>
       </c>
       <c r="R19" t="n">
-        <v>6523735</v>
+        <v>6523853</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2640,10 +2632,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128068263</v>
+        <v>128068256</v>
       </c>
       <c r="B20" t="n">
-        <v>96835</v>
+        <v>96837</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2675,10 +2667,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>312975</v>
+        <v>312927</v>
       </c>
       <c r="R20" t="n">
-        <v>6523853</v>
+        <v>6523972</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2737,10 +2729,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128068256</v>
+        <v>128068272</v>
       </c>
       <c r="B21" t="n">
-        <v>96835</v>
+        <v>57686</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2748,34 +2740,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>312927</v>
+        <v>312856</v>
       </c>
       <c r="R21" t="n">
-        <v>6523972</v>
+        <v>6523735</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2837,7 +2837,7 @@
         <v>128068251</v>
       </c>
       <c r="B22" t="n">
-        <v>96835</v>
+        <v>96837</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>128068255</v>
       </c>
       <c r="B23" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3043,10 +3043,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128068245</v>
+        <v>128068269</v>
       </c>
       <c r="B24" t="n">
-        <v>5197</v>
+        <v>4779</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3054,34 +3054,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>105930</v>
+        <v>102306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>312898</v>
+        <v>312859</v>
       </c>
       <c r="R24" t="n">
-        <v>6524038</v>
+        <v>6523647</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3155,10 +3160,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128068266</v>
+        <v>128068245</v>
       </c>
       <c r="B25" t="n">
-        <v>8450</v>
+        <v>5197</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3166,39 +3171,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>105930</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>312948</v>
+        <v>312898</v>
       </c>
       <c r="R25" t="n">
-        <v>6523764</v>
+        <v>6524038</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3244,17 +3244,17 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3272,10 +3272,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128068269</v>
+        <v>128068266</v>
       </c>
       <c r="B26" t="n">
-        <v>4779</v>
+        <v>8450</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3283,27 +3283,27 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102306</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3312,10 +3312,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>312859</v>
+        <v>312948</v>
       </c>
       <c r="R26" t="n">
-        <v>6523647</v>
+        <v>6523764</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3361,17 +3361,17 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3392,7 +3392,7 @@
         <v>128068270</v>
       </c>
       <c r="B27" t="n">
-        <v>75113</v>
+        <v>75115</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3501,10 +3501,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128068238</v>
+        <v>128068248</v>
       </c>
       <c r="B28" t="n">
-        <v>56880</v>
+        <v>91431</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3512,38 +3512,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>312809</v>
+        <v>313036</v>
       </c>
       <c r="R28" t="n">
-        <v>6524225</v>
+        <v>6523992</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3586,6 +3582,21 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3602,32 +3613,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128068248</v>
+        <v>128068241</v>
       </c>
       <c r="B29" t="n">
-        <v>91429</v>
+        <v>91486</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>5442</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3637,10 +3648,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>313036</v>
+        <v>312717</v>
       </c>
       <c r="R29" t="n">
-        <v>6523992</v>
+        <v>6524079</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3686,17 +3697,17 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3714,32 +3725,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128068241</v>
+        <v>128068253</v>
       </c>
       <c r="B30" t="n">
-        <v>91484</v>
+        <v>91450</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5442</v>
+        <v>4660</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3749,10 +3760,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>312717</v>
+        <v>313007</v>
       </c>
       <c r="R30" t="n">
-        <v>6524079</v>
+        <v>6523966</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3798,17 +3809,17 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3826,10 +3837,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128068253</v>
+        <v>128068238</v>
       </c>
       <c r="B31" t="n">
-        <v>91448</v>
+        <v>56880</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3837,34 +3848,38 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4660</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>313007</v>
+        <v>312809</v>
       </c>
       <c r="R31" t="n">
-        <v>6523966</v>
+        <v>6524225</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3907,21 +3922,6 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -3941,7 +3941,7 @@
         <v>128068260</v>
       </c>
       <c r="B32" t="n">
-        <v>91517</v>
+        <v>91519</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4054,7 +4054,7 @@
         <v>128068252</v>
       </c>
       <c r="B33" t="n">
-        <v>75113</v>
+        <v>75115</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 35468-2025 artfynd.xlsx
+++ b/artfynd/A 35468-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AY49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4161,6 +4161,1732 @@
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>128877195</v>
+      </c>
+      <c r="B34" t="n">
+        <v>92982</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Keddebo, Boh</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>312907</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6523918</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>128877203</v>
+      </c>
+      <c r="B35" t="n">
+        <v>92982</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Keddebo, Boh</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>312756</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6524245</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>128877167</v>
+      </c>
+      <c r="B36" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Keddebo, Boh</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>312765</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6523969</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>128877166</v>
+      </c>
+      <c r="B37" t="n">
+        <v>90277</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>1596</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Jättemusseron</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Tricholoma colossus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Keddebo, Boh</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>312630</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6524301</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>128877168</v>
+      </c>
+      <c r="B38" t="n">
+        <v>78877</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Keddebo, Boh</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>312765</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6523969</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>128877172</v>
+      </c>
+      <c r="B39" t="n">
+        <v>4779</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Keddebo, Boh</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>312863</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6523631</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>128877201</v>
+      </c>
+      <c r="B40" t="n">
+        <v>96907</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>2590</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Odontoschisma denudatum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Keddebo, Boh</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>312904</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6524032</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>128877191</v>
+      </c>
+      <c r="B41" t="n">
+        <v>80785</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Keddebo, Boh</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>312882</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6523636</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>klibbal</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>128877199</v>
+      </c>
+      <c r="B42" t="n">
+        <v>96907</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>2590</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Odontoschisma denudatum</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Keddebo, Boh</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>312880</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6523963</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>128877192</v>
+      </c>
+      <c r="B43" t="n">
+        <v>92789</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Keddebo, Boh</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>312952</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6523854</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>128877196</v>
+      </c>
+      <c r="B44" t="n">
+        <v>92982</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Keddebo, Boh</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>312874</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6523945</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>128877194</v>
+      </c>
+      <c r="B45" t="n">
+        <v>92789</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Keddebo, Boh</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>312901</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6523903</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>128877202</v>
+      </c>
+      <c r="B46" t="n">
+        <v>75143</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Keddebo, Boh</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>312754</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6524211</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>128877170</v>
+      </c>
+      <c r="B47" t="n">
+        <v>5197</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Keddebo, Boh</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>312863</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6523631</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>128877198</v>
+      </c>
+      <c r="B48" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Keddebo, Boh</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>312874</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6523945</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>128877204</v>
+      </c>
+      <c r="B49" t="n">
+        <v>92789</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Keddebo, Boh</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>312745</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6524371</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Krokstad</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35468-2025 artfynd.xlsx
+++ b/artfynd/A 35468-2025 artfynd.xlsx
@@ -4166,7 +4166,7 @@
         <v>128877195</v>
       </c>
       <c r="B34" t="n">
-        <v>92982</v>
+        <v>92989</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>128877203</v>
       </c>
       <c r="B35" t="n">
-        <v>92982</v>
+        <v>92989</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4507,7 +4507,7 @@
         <v>128877166</v>
       </c>
       <c r="B37" t="n">
-        <v>90277</v>
+        <v>90282</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4717,10 +4717,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128877172</v>
+        <v>128877201</v>
       </c>
       <c r="B39" t="n">
-        <v>4779</v>
+        <v>96914</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4728,39 +4728,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>102306</v>
+        <v>2590</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>312863</v>
+        <v>312904</v>
       </c>
       <c r="R39" t="n">
-        <v>6523631</v>
+        <v>6524032</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4803,21 +4798,6 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -4834,10 +4814,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128877201</v>
+        <v>128877172</v>
       </c>
       <c r="B40" t="n">
-        <v>96907</v>
+        <v>4779</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4845,34 +4825,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2590</v>
+        <v>102306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>312904</v>
+        <v>312863</v>
       </c>
       <c r="R40" t="n">
-        <v>6524032</v>
+        <v>6523631</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4915,6 +4900,21 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5046,7 +5046,7 @@
         <v>128877199</v>
       </c>
       <c r="B42" t="n">
-        <v>96907</v>
+        <v>96914</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         <v>128877192</v>
       </c>
       <c r="B43" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5237,32 +5237,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128877196</v>
+        <v>128877194</v>
       </c>
       <c r="B44" t="n">
-        <v>92982</v>
+        <v>92794</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5272,10 +5272,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>312874</v>
+        <v>312901</v>
       </c>
       <c r="R44" t="n">
-        <v>6523945</v>
+        <v>6523903</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5318,21 +5318,6 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5349,32 +5334,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128877194</v>
+        <v>128877196</v>
       </c>
       <c r="B45" t="n">
-        <v>92789</v>
+        <v>92989</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5384,10 +5369,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>312901</v>
+        <v>312874</v>
       </c>
       <c r="R45" t="n">
-        <v>6523903</v>
+        <v>6523945</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5430,6 +5415,21 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5446,10 +5446,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128877202</v>
+        <v>128877170</v>
       </c>
       <c r="B46" t="n">
-        <v>75143</v>
+        <v>5197</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5457,34 +5457,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6426</v>
+        <v>105930</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>312754</v>
+        <v>312863</v>
       </c>
       <c r="R46" t="n">
-        <v>6524211</v>
+        <v>6523631</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5558,10 +5563,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128877170</v>
+        <v>128877202</v>
       </c>
       <c r="B47" t="n">
-        <v>5197</v>
+        <v>75143</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5569,39 +5574,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>105930</v>
+        <v>6426</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>312863</v>
+        <v>312754</v>
       </c>
       <c r="R47" t="n">
-        <v>6523631</v>
+        <v>6524211</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5795,7 +5795,7 @@
         <v>128877204</v>
       </c>
       <c r="B49" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 35468-2025 artfynd.xlsx
+++ b/artfynd/A 35468-2025 artfynd.xlsx
@@ -5140,32 +5140,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128877192</v>
+        <v>128877196</v>
       </c>
       <c r="B43" t="n">
-        <v>92794</v>
+        <v>92989</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5175,10 +5175,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>312952</v>
+        <v>312874</v>
       </c>
       <c r="R43" t="n">
-        <v>6523854</v>
+        <v>6523945</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5221,6 +5221,21 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5237,7 +5252,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128877194</v>
+        <v>128877192</v>
       </c>
       <c r="B44" t="n">
         <v>92794</v>
@@ -5272,10 +5287,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>312901</v>
+        <v>312952</v>
       </c>
       <c r="R44" t="n">
-        <v>6523903</v>
+        <v>6523854</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5334,32 +5349,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128877196</v>
+        <v>128877194</v>
       </c>
       <c r="B45" t="n">
-        <v>92989</v>
+        <v>92794</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5369,10 +5384,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>312874</v>
+        <v>312901</v>
       </c>
       <c r="R45" t="n">
-        <v>6523945</v>
+        <v>6523903</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5415,21 +5430,6 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5446,10 +5446,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128877170</v>
+        <v>128877202</v>
       </c>
       <c r="B46" t="n">
-        <v>5197</v>
+        <v>75143</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5457,39 +5457,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>105930</v>
+        <v>6426</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>312863</v>
+        <v>312754</v>
       </c>
       <c r="R46" t="n">
-        <v>6523631</v>
+        <v>6524211</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5563,10 +5558,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128877202</v>
+        <v>128877170</v>
       </c>
       <c r="B47" t="n">
-        <v>75143</v>
+        <v>5197</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5574,34 +5569,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6426</v>
+        <v>105930</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>312754</v>
+        <v>312863</v>
       </c>
       <c r="R47" t="n">
-        <v>6524211</v>
+        <v>6523631</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>

--- a/artfynd/A 35468-2025 artfynd.xlsx
+++ b/artfynd/A 35468-2025 artfynd.xlsx
@@ -4717,10 +4717,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128877201</v>
+        <v>128877172</v>
       </c>
       <c r="B39" t="n">
-        <v>96914</v>
+        <v>4779</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4728,34 +4728,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2590</v>
+        <v>102306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>312904</v>
+        <v>312863</v>
       </c>
       <c r="R39" t="n">
-        <v>6524032</v>
+        <v>6523631</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4798,6 +4803,21 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -4814,10 +4834,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128877172</v>
+        <v>128877201</v>
       </c>
       <c r="B40" t="n">
-        <v>4779</v>
+        <v>96914</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4825,39 +4845,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>102306</v>
+        <v>2590</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>312863</v>
+        <v>312904</v>
       </c>
       <c r="R40" t="n">
-        <v>6523631</v>
+        <v>6524032</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4900,21 +4915,6 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5140,32 +5140,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128877196</v>
+        <v>128877192</v>
       </c>
       <c r="B43" t="n">
-        <v>92989</v>
+        <v>92794</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5175,10 +5175,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>312874</v>
+        <v>312952</v>
       </c>
       <c r="R43" t="n">
-        <v>6523945</v>
+        <v>6523854</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5221,21 +5221,6 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5252,7 +5237,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128877192</v>
+        <v>128877194</v>
       </c>
       <c r="B44" t="n">
         <v>92794</v>
@@ -5287,10 +5272,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>312952</v>
+        <v>312901</v>
       </c>
       <c r="R44" t="n">
-        <v>6523854</v>
+        <v>6523903</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5349,32 +5334,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128877194</v>
+        <v>128877196</v>
       </c>
       <c r="B45" t="n">
-        <v>92794</v>
+        <v>92989</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5384,10 +5369,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>312901</v>
+        <v>312874</v>
       </c>
       <c r="R45" t="n">
-        <v>6523903</v>
+        <v>6523945</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5430,6 +5415,21 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5446,10 +5446,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128877202</v>
+        <v>128877170</v>
       </c>
       <c r="B46" t="n">
-        <v>75143</v>
+        <v>5197</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5457,34 +5457,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6426</v>
+        <v>105930</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>312754</v>
+        <v>312863</v>
       </c>
       <c r="R46" t="n">
-        <v>6524211</v>
+        <v>6523631</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5558,10 +5563,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128877170</v>
+        <v>128877202</v>
       </c>
       <c r="B47" t="n">
-        <v>5197</v>
+        <v>75143</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5569,39 +5574,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>105930</v>
+        <v>6426</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>312863</v>
+        <v>312754</v>
       </c>
       <c r="R47" t="n">
-        <v>6523631</v>
+        <v>6524211</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>

--- a/artfynd/A 35468-2025 artfynd.xlsx
+++ b/artfynd/A 35468-2025 artfynd.xlsx
@@ -4166,7 +4166,7 @@
         <v>128877195</v>
       </c>
       <c r="B34" t="n">
-        <v>92989</v>
+        <v>92993</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>128877203</v>
       </c>
       <c r="B35" t="n">
-        <v>92989</v>
+        <v>92993</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4507,7 +4507,7 @@
         <v>128877166</v>
       </c>
       <c r="B37" t="n">
-        <v>90282</v>
+        <v>90286</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>128877168</v>
       </c>
       <c r="B38" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4834,10 +4834,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128877201</v>
+        <v>128877191</v>
       </c>
       <c r="B40" t="n">
-        <v>96914</v>
+        <v>80789</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4845,21 +4845,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2590</v>
+        <v>230185</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4869,10 +4869,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>312904</v>
+        <v>312882</v>
       </c>
       <c r="R40" t="n">
-        <v>6524032</v>
+        <v>6523636</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4915,6 +4915,21 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>klibbal</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -4931,10 +4946,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128877191</v>
+        <v>128877201</v>
       </c>
       <c r="B41" t="n">
-        <v>80785</v>
+        <v>96918</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4942,21 +4957,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>230185</v>
+        <v>2590</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4966,10 +4981,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>312882</v>
+        <v>312904</v>
       </c>
       <c r="R41" t="n">
-        <v>6523636</v>
+        <v>6524032</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5012,21 +5027,6 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>klibbal</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Alnus glutinosa</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Alnus glutinosa</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5046,7 +5046,7 @@
         <v>128877199</v>
       </c>
       <c r="B42" t="n">
-        <v>96914</v>
+        <v>96918</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5140,32 +5140,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128877192</v>
+        <v>128877196</v>
       </c>
       <c r="B43" t="n">
-        <v>92794</v>
+        <v>92993</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5175,10 +5175,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>312952</v>
+        <v>312874</v>
       </c>
       <c r="R43" t="n">
-        <v>6523854</v>
+        <v>6523945</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5221,6 +5221,21 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5240,7 +5255,7 @@
         <v>128877194</v>
       </c>
       <c r="B44" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5334,32 +5349,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128877196</v>
+        <v>128877192</v>
       </c>
       <c r="B45" t="n">
-        <v>92989</v>
+        <v>92798</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5369,10 +5384,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>312874</v>
+        <v>312952</v>
       </c>
       <c r="R45" t="n">
-        <v>6523945</v>
+        <v>6523854</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5415,21 +5430,6 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5446,10 +5446,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128877170</v>
+        <v>128877202</v>
       </c>
       <c r="B46" t="n">
-        <v>5197</v>
+        <v>75147</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5457,39 +5457,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>105930</v>
+        <v>6426</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>312863</v>
+        <v>312754</v>
       </c>
       <c r="R46" t="n">
-        <v>6523631</v>
+        <v>6524211</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5563,10 +5558,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128877202</v>
+        <v>128877170</v>
       </c>
       <c r="B47" t="n">
-        <v>75143</v>
+        <v>5197</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5574,34 +5569,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6426</v>
+        <v>105930</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>312754</v>
+        <v>312863</v>
       </c>
       <c r="R47" t="n">
-        <v>6524211</v>
+        <v>6523631</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5795,7 +5795,7 @@
         <v>128877204</v>
       </c>
       <c r="B49" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 35468-2025 artfynd.xlsx
+++ b/artfynd/A 35468-2025 artfynd.xlsx
@@ -4275,45 +4275,50 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128877203</v>
+        <v>128877167</v>
       </c>
       <c r="B35" t="n">
-        <v>92993</v>
+        <v>8450</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2079</v>
+        <v>106545</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>312756</v>
+        <v>312765</v>
       </c>
       <c r="R35" t="n">
-        <v>6524245</v>
+        <v>6523969</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4387,50 +4392,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128877167</v>
+        <v>128877203</v>
       </c>
       <c r="B36" t="n">
-        <v>8450</v>
+        <v>92993</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106545</v>
+        <v>2079</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>312765</v>
+        <v>312756</v>
       </c>
       <c r="R36" t="n">
-        <v>6523969</v>
+        <v>6524245</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -5140,32 +5140,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128877196</v>
+        <v>128877192</v>
       </c>
       <c r="B43" t="n">
-        <v>92993</v>
+        <v>92798</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5175,10 +5175,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>312874</v>
+        <v>312952</v>
       </c>
       <c r="R43" t="n">
-        <v>6523945</v>
+        <v>6523854</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5221,21 +5221,6 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5349,32 +5334,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128877192</v>
+        <v>128877196</v>
       </c>
       <c r="B45" t="n">
-        <v>92798</v>
+        <v>92993</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5384,10 +5369,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>312952</v>
+        <v>312874</v>
       </c>
       <c r="R45" t="n">
-        <v>6523854</v>
+        <v>6523945</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5430,6 +5415,21 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5446,10 +5446,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128877202</v>
+        <v>128877170</v>
       </c>
       <c r="B46" t="n">
-        <v>75147</v>
+        <v>5197</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5457,34 +5457,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6426</v>
+        <v>105930</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>312754</v>
+        <v>312863</v>
       </c>
       <c r="R46" t="n">
-        <v>6524211</v>
+        <v>6523631</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5558,10 +5563,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128877170</v>
+        <v>128877202</v>
       </c>
       <c r="B47" t="n">
-        <v>5197</v>
+        <v>75147</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5569,39 +5574,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>105930</v>
+        <v>6426</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>312863</v>
+        <v>312754</v>
       </c>
       <c r="R47" t="n">
-        <v>6523631</v>
+        <v>6524211</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5675,10 +5675,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128877198</v>
+        <v>128877204</v>
       </c>
       <c r="B48" t="n">
-        <v>8450</v>
+        <v>92798</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5686,39 +5686,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>312874</v>
+        <v>312745</v>
       </c>
       <c r="R48" t="n">
-        <v>6523945</v>
+        <v>6524371</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5761,21 +5756,6 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -5792,10 +5772,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128877204</v>
+        <v>128877198</v>
       </c>
       <c r="B49" t="n">
-        <v>92798</v>
+        <v>8450</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5803,34 +5783,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>312745</v>
+        <v>312874</v>
       </c>
       <c r="R49" t="n">
-        <v>6524371</v>
+        <v>6523945</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5873,6 +5858,21 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">

--- a/artfynd/A 35468-2025 artfynd.xlsx
+++ b/artfynd/A 35468-2025 artfynd.xlsx
@@ -4275,50 +4275,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128877167</v>
+        <v>128877203</v>
       </c>
       <c r="B35" t="n">
-        <v>8450</v>
+        <v>92993</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106545</v>
+        <v>2079</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>312765</v>
+        <v>312756</v>
       </c>
       <c r="R35" t="n">
-        <v>6523969</v>
+        <v>6524245</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4392,45 +4387,50 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128877203</v>
+        <v>128877167</v>
       </c>
       <c r="B36" t="n">
-        <v>92993</v>
+        <v>8450</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2079</v>
+        <v>106545</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>312756</v>
+        <v>312765</v>
       </c>
       <c r="R36" t="n">
-        <v>6524245</v>
+        <v>6523969</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4717,10 +4717,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128877172</v>
+        <v>128877191</v>
       </c>
       <c r="B39" t="n">
-        <v>4779</v>
+        <v>80789</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4728,39 +4728,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>102306</v>
+        <v>230185</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>312863</v>
+        <v>312882</v>
       </c>
       <c r="R39" t="n">
-        <v>6523631</v>
+        <v>6523636</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4806,17 +4801,17 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>klibbal</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Alnus glutinosa</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Alnus glutinosa</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -4834,10 +4829,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128877191</v>
+        <v>128877201</v>
       </c>
       <c r="B40" t="n">
-        <v>80789</v>
+        <v>96918</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4845,21 +4840,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>230185</v>
+        <v>2590</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4869,10 +4864,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>312882</v>
+        <v>312904</v>
       </c>
       <c r="R40" t="n">
-        <v>6523636</v>
+        <v>6524032</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4915,21 +4910,6 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>klibbal</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Alnus glutinosa</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Alnus glutinosa</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -4946,10 +4926,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128877201</v>
+        <v>128877172</v>
       </c>
       <c r="B41" t="n">
-        <v>96918</v>
+        <v>4779</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4957,34 +4937,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2590</v>
+        <v>102306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>312904</v>
+        <v>312863</v>
       </c>
       <c r="R41" t="n">
-        <v>6524032</v>
+        <v>6523631</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5027,6 +5012,21 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5140,32 +5140,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128877192</v>
+        <v>128877196</v>
       </c>
       <c r="B43" t="n">
-        <v>92798</v>
+        <v>92993</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5175,10 +5175,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>312952</v>
+        <v>312874</v>
       </c>
       <c r="R43" t="n">
-        <v>6523854</v>
+        <v>6523945</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5221,6 +5221,21 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5237,7 +5252,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128877194</v>
+        <v>128877192</v>
       </c>
       <c r="B44" t="n">
         <v>92798</v>
@@ -5272,10 +5287,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>312901</v>
+        <v>312952</v>
       </c>
       <c r="R44" t="n">
-        <v>6523903</v>
+        <v>6523854</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5334,32 +5349,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128877196</v>
+        <v>128877194</v>
       </c>
       <c r="B45" t="n">
-        <v>92993</v>
+        <v>92798</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5369,10 +5384,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>312874</v>
+        <v>312901</v>
       </c>
       <c r="R45" t="n">
-        <v>6523945</v>
+        <v>6523903</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5415,21 +5430,6 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5446,10 +5446,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128877170</v>
+        <v>128877202</v>
       </c>
       <c r="B46" t="n">
-        <v>5197</v>
+        <v>75147</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5457,39 +5457,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>105930</v>
+        <v>6426</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>312863</v>
+        <v>312754</v>
       </c>
       <c r="R46" t="n">
-        <v>6523631</v>
+        <v>6524211</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5563,10 +5558,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128877202</v>
+        <v>128877170</v>
       </c>
       <c r="B47" t="n">
-        <v>75147</v>
+        <v>5197</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5574,34 +5569,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6426</v>
+        <v>105930</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>312754</v>
+        <v>312863</v>
       </c>
       <c r="R47" t="n">
-        <v>6524211</v>
+        <v>6523631</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5675,10 +5675,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128877204</v>
+        <v>128877198</v>
       </c>
       <c r="B48" t="n">
-        <v>92798</v>
+        <v>8450</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5686,34 +5686,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>312745</v>
+        <v>312874</v>
       </c>
       <c r="R48" t="n">
-        <v>6524371</v>
+        <v>6523945</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5756,6 +5761,21 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -5772,10 +5792,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128877198</v>
+        <v>128877204</v>
       </c>
       <c r="B49" t="n">
-        <v>8450</v>
+        <v>92798</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5783,39 +5803,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>312874</v>
+        <v>312745</v>
       </c>
       <c r="R49" t="n">
-        <v>6523945</v>
+        <v>6524371</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5858,21 +5873,6 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">

--- a/artfynd/A 35468-2025 artfynd.xlsx
+++ b/artfynd/A 35468-2025 artfynd.xlsx
@@ -4166,7 +4166,7 @@
         <v>128877195</v>
       </c>
       <c r="B34" t="n">
-        <v>92993</v>
+        <v>92998</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>128877203</v>
       </c>
       <c r="B35" t="n">
-        <v>92993</v>
+        <v>92998</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4507,7 +4507,7 @@
         <v>128877166</v>
       </c>
       <c r="B37" t="n">
-        <v>90286</v>
+        <v>90291</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>128877168</v>
       </c>
       <c r="B38" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4717,10 +4717,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128877191</v>
+        <v>128877172</v>
       </c>
       <c r="B39" t="n">
-        <v>80789</v>
+        <v>4779</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4728,34 +4728,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>230185</v>
+        <v>102306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>312882</v>
+        <v>312863</v>
       </c>
       <c r="R39" t="n">
-        <v>6523636</v>
+        <v>6523631</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4801,17 +4806,17 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>klibbal</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>Alnus glutinosa</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Alnus glutinosa</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -4832,7 +4837,7 @@
         <v>128877201</v>
       </c>
       <c r="B40" t="n">
-        <v>96918</v>
+        <v>96925</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4926,10 +4931,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128877172</v>
+        <v>128877191</v>
       </c>
       <c r="B41" t="n">
-        <v>4779</v>
+        <v>80694</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4937,39 +4942,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>102306</v>
+        <v>230185</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>312863</v>
+        <v>312882</v>
       </c>
       <c r="R41" t="n">
-        <v>6523631</v>
+        <v>6523636</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5015,17 +5015,17 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>klibbal</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Alnus glutinosa</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Alnus glutinosa</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5046,7 +5046,7 @@
         <v>128877199</v>
       </c>
       <c r="B42" t="n">
-        <v>96918</v>
+        <v>96925</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         <v>128877196</v>
       </c>
       <c r="B43" t="n">
-        <v>92993</v>
+        <v>92998</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5255,7 +5255,7 @@
         <v>128877192</v>
       </c>
       <c r="B44" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5352,7 +5352,7 @@
         <v>128877194</v>
       </c>
       <c r="B45" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5446,10 +5446,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128877202</v>
+        <v>128877170</v>
       </c>
       <c r="B46" t="n">
-        <v>75147</v>
+        <v>5197</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5457,34 +5457,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6426</v>
+        <v>105930</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>312754</v>
+        <v>312863</v>
       </c>
       <c r="R46" t="n">
-        <v>6524211</v>
+        <v>6523631</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5558,10 +5563,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128877170</v>
+        <v>128877202</v>
       </c>
       <c r="B47" t="n">
-        <v>5197</v>
+        <v>75150</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5569,39 +5574,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>105930</v>
+        <v>6426</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>312863</v>
+        <v>312754</v>
       </c>
       <c r="R47" t="n">
-        <v>6523631</v>
+        <v>6524211</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5675,10 +5675,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128877198</v>
+        <v>128877204</v>
       </c>
       <c r="B48" t="n">
-        <v>8450</v>
+        <v>92803</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5686,39 +5686,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>312874</v>
+        <v>312745</v>
       </c>
       <c r="R48" t="n">
-        <v>6523945</v>
+        <v>6524371</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5761,21 +5756,6 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -5792,10 +5772,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128877204</v>
+        <v>128877198</v>
       </c>
       <c r="B49" t="n">
-        <v>92798</v>
+        <v>8450</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5803,34 +5783,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>312745</v>
+        <v>312874</v>
       </c>
       <c r="R49" t="n">
-        <v>6524371</v>
+        <v>6523945</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5873,6 +5858,21 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">

--- a/artfynd/A 35468-2025 artfynd.xlsx
+++ b/artfynd/A 35468-2025 artfynd.xlsx
@@ -4717,10 +4717,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128877172</v>
+        <v>128877201</v>
       </c>
       <c r="B39" t="n">
-        <v>4779</v>
+        <v>96933</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4728,39 +4728,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>102306</v>
+        <v>2590</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>312863</v>
+        <v>312904</v>
       </c>
       <c r="R39" t="n">
-        <v>6523631</v>
+        <v>6524032</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4803,21 +4798,6 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -4834,10 +4814,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128877201</v>
+        <v>128877172</v>
       </c>
       <c r="B40" t="n">
-        <v>96933</v>
+        <v>4779</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4845,34 +4825,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2590</v>
+        <v>102306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>312904</v>
+        <v>312863</v>
       </c>
       <c r="R40" t="n">
-        <v>6524032</v>
+        <v>6523631</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4915,6 +4900,21 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5675,10 +5675,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128877204</v>
+        <v>128877198</v>
       </c>
       <c r="B48" t="n">
-        <v>92811</v>
+        <v>8450</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5686,34 +5686,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>312745</v>
+        <v>312874</v>
       </c>
       <c r="R48" t="n">
-        <v>6524371</v>
+        <v>6523945</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5756,6 +5761,21 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -5772,10 +5792,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128877198</v>
+        <v>128877204</v>
       </c>
       <c r="B49" t="n">
-        <v>8450</v>
+        <v>92811</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5783,39 +5803,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>312874</v>
+        <v>312745</v>
       </c>
       <c r="R49" t="n">
-        <v>6523945</v>
+        <v>6524371</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5858,21 +5873,6 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">

--- a/artfynd/A 35468-2025 artfynd.xlsx
+++ b/artfynd/A 35468-2025 artfynd.xlsx
@@ -4166,7 +4166,7 @@
         <v>128877195</v>
       </c>
       <c r="B34" t="n">
-        <v>93006</v>
+        <v>93011</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4275,50 +4275,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128877167</v>
+        <v>128877203</v>
       </c>
       <c r="B35" t="n">
-        <v>8450</v>
+        <v>93011</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106545</v>
+        <v>2079</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>312765</v>
+        <v>312756</v>
       </c>
       <c r="R35" t="n">
-        <v>6523969</v>
+        <v>6524245</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4392,45 +4387,50 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128877203</v>
+        <v>128877167</v>
       </c>
       <c r="B36" t="n">
-        <v>93006</v>
+        <v>8450</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2079</v>
+        <v>106545</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>312756</v>
+        <v>312765</v>
       </c>
       <c r="R36" t="n">
-        <v>6524245</v>
+        <v>6523969</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4507,7 +4507,7 @@
         <v>128877166</v>
       </c>
       <c r="B37" t="n">
-        <v>90298</v>
+        <v>90301</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4717,10 +4717,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128877201</v>
+        <v>128877172</v>
       </c>
       <c r="B39" t="n">
-        <v>96933</v>
+        <v>4779</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4728,34 +4728,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2590</v>
+        <v>102306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>312904</v>
+        <v>312863</v>
       </c>
       <c r="R39" t="n">
-        <v>6524032</v>
+        <v>6523631</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4798,6 +4803,21 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -4814,10 +4834,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128877172</v>
+        <v>128877201</v>
       </c>
       <c r="B40" t="n">
-        <v>4779</v>
+        <v>96938</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4825,39 +4845,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>102306</v>
+        <v>2590</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>312863</v>
+        <v>312904</v>
       </c>
       <c r="R40" t="n">
-        <v>6523631</v>
+        <v>6524032</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4900,21 +4915,6 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5046,7 +5046,7 @@
         <v>128877199</v>
       </c>
       <c r="B42" t="n">
-        <v>96933</v>
+        <v>96938</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         <v>128877192</v>
       </c>
       <c r="B43" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5240,7 +5240,7 @@
         <v>128877194</v>
       </c>
       <c r="B44" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5337,7 +5337,7 @@
         <v>128877196</v>
       </c>
       <c r="B45" t="n">
-        <v>93006</v>
+        <v>93011</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5446,10 +5446,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128877170</v>
+        <v>128877202</v>
       </c>
       <c r="B46" t="n">
-        <v>5197</v>
+        <v>75155</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5457,39 +5457,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>105930</v>
+        <v>6426</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>312863</v>
+        <v>312754</v>
       </c>
       <c r="R46" t="n">
-        <v>6523631</v>
+        <v>6524211</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5563,10 +5558,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128877202</v>
+        <v>128877170</v>
       </c>
       <c r="B47" t="n">
-        <v>75155</v>
+        <v>5197</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5574,34 +5569,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6426</v>
+        <v>105930</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>312754</v>
+        <v>312863</v>
       </c>
       <c r="R47" t="n">
-        <v>6524211</v>
+        <v>6523631</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5675,10 +5675,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128877198</v>
+        <v>128877204</v>
       </c>
       <c r="B48" t="n">
-        <v>8450</v>
+        <v>92816</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5686,39 +5686,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>312874</v>
+        <v>312745</v>
       </c>
       <c r="R48" t="n">
-        <v>6523945</v>
+        <v>6524371</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5761,21 +5756,6 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -5792,10 +5772,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128877204</v>
+        <v>128877198</v>
       </c>
       <c r="B49" t="n">
-        <v>92811</v>
+        <v>8450</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5803,34 +5783,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>312745</v>
+        <v>312874</v>
       </c>
       <c r="R49" t="n">
-        <v>6524371</v>
+        <v>6523945</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5873,6 +5858,21 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">

--- a/artfynd/A 35468-2025 artfynd.xlsx
+++ b/artfynd/A 35468-2025 artfynd.xlsx
@@ -4166,7 +4166,7 @@
         <v>128877195</v>
       </c>
       <c r="B34" t="n">
-        <v>93011</v>
+        <v>93014</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>128877203</v>
       </c>
       <c r="B35" t="n">
-        <v>93011</v>
+        <v>93014</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4507,7 +4507,7 @@
         <v>128877166</v>
       </c>
       <c r="B37" t="n">
-        <v>90301</v>
+        <v>90304</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>128877168</v>
       </c>
       <c r="B38" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4837,7 +4837,7 @@
         <v>128877201</v>
       </c>
       <c r="B40" t="n">
-        <v>96938</v>
+        <v>96941</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4934,7 +4934,7 @@
         <v>128877191</v>
       </c>
       <c r="B41" t="n">
-        <v>80699</v>
+        <v>80700</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
         <v>128877199</v>
       </c>
       <c r="B42" t="n">
-        <v>96938</v>
+        <v>96941</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5140,32 +5140,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128877192</v>
+        <v>128877196</v>
       </c>
       <c r="B43" t="n">
-        <v>92816</v>
+        <v>93014</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5175,10 +5175,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>312952</v>
+        <v>312874</v>
       </c>
       <c r="R43" t="n">
-        <v>6523854</v>
+        <v>6523945</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5221,6 +5221,21 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5237,10 +5252,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128877194</v>
+        <v>128877192</v>
       </c>
       <c r="B44" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5272,10 +5287,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>312901</v>
+        <v>312952</v>
       </c>
       <c r="R44" t="n">
-        <v>6523903</v>
+        <v>6523854</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5334,32 +5349,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128877196</v>
+        <v>128877194</v>
       </c>
       <c r="B45" t="n">
-        <v>93011</v>
+        <v>92819</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5369,10 +5384,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>312874</v>
+        <v>312901</v>
       </c>
       <c r="R45" t="n">
-        <v>6523945</v>
+        <v>6523903</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5415,21 +5430,6 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5678,7 +5678,7 @@
         <v>128877204</v>
       </c>
       <c r="B48" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 35468-2025 artfynd.xlsx
+++ b/artfynd/A 35468-2025 artfynd.xlsx
@@ -4275,45 +4275,50 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128877203</v>
+        <v>128877167</v>
       </c>
       <c r="B35" t="n">
-        <v>93014</v>
+        <v>8450</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2079</v>
+        <v>106545</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>312756</v>
+        <v>312765</v>
       </c>
       <c r="R35" t="n">
-        <v>6524245</v>
+        <v>6523969</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4387,50 +4392,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128877167</v>
+        <v>128877203</v>
       </c>
       <c r="B36" t="n">
-        <v>8450</v>
+        <v>93014</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106545</v>
+        <v>2079</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>312765</v>
+        <v>312756</v>
       </c>
       <c r="R36" t="n">
-        <v>6523969</v>
+        <v>6524245</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4717,10 +4717,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128877172</v>
+        <v>128877201</v>
       </c>
       <c r="B39" t="n">
-        <v>4779</v>
+        <v>96941</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4728,39 +4728,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>102306</v>
+        <v>2590</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>312863</v>
+        <v>312904</v>
       </c>
       <c r="R39" t="n">
-        <v>6523631</v>
+        <v>6524032</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4803,21 +4798,6 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -4834,10 +4814,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128877201</v>
+        <v>128877172</v>
       </c>
       <c r="B40" t="n">
-        <v>96941</v>
+        <v>4779</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4845,34 +4825,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2590</v>
+        <v>102306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>312904</v>
+        <v>312863</v>
       </c>
       <c r="R40" t="n">
-        <v>6524032</v>
+        <v>6523631</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4915,6 +4900,21 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">

--- a/artfynd/A 35468-2025 artfynd.xlsx
+++ b/artfynd/A 35468-2025 artfynd.xlsx
@@ -4275,50 +4275,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128877167</v>
+        <v>128877203</v>
       </c>
       <c r="B35" t="n">
-        <v>8450</v>
+        <v>93014</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106545</v>
+        <v>2079</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>312765</v>
+        <v>312756</v>
       </c>
       <c r="R35" t="n">
-        <v>6523969</v>
+        <v>6524245</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4392,45 +4387,50 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128877203</v>
+        <v>128877167</v>
       </c>
       <c r="B36" t="n">
-        <v>93014</v>
+        <v>8450</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2079</v>
+        <v>106545</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>312756</v>
+        <v>312765</v>
       </c>
       <c r="R36" t="n">
-        <v>6524245</v>
+        <v>6523969</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>

--- a/artfynd/A 35468-2025 artfynd.xlsx
+++ b/artfynd/A 35468-2025 artfynd.xlsx
@@ -4275,45 +4275,50 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128877203</v>
+        <v>128877167</v>
       </c>
       <c r="B35" t="n">
-        <v>93014</v>
+        <v>8450</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2079</v>
+        <v>106545</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>312756</v>
+        <v>312765</v>
       </c>
       <c r="R35" t="n">
-        <v>6524245</v>
+        <v>6523969</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4387,50 +4392,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128877167</v>
+        <v>128877203</v>
       </c>
       <c r="B36" t="n">
-        <v>8450</v>
+        <v>93014</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106545</v>
+        <v>2079</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>312765</v>
+        <v>312756</v>
       </c>
       <c r="R36" t="n">
-        <v>6523969</v>
+        <v>6524245</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4814,10 +4814,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128877172</v>
+        <v>128877191</v>
       </c>
       <c r="B40" t="n">
-        <v>4779</v>
+        <v>80700</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4825,39 +4825,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>102306</v>
+        <v>230185</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>312863</v>
+        <v>312882</v>
       </c>
       <c r="R40" t="n">
-        <v>6523631</v>
+        <v>6523636</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4903,17 +4898,17 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>klibbal</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Alnus glutinosa</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Alnus glutinosa</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -4931,10 +4926,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128877191</v>
+        <v>128877172</v>
       </c>
       <c r="B41" t="n">
-        <v>80700</v>
+        <v>4779</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4942,34 +4937,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>230185</v>
+        <v>102306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>312882</v>
+        <v>312863</v>
       </c>
       <c r="R41" t="n">
-        <v>6523636</v>
+        <v>6523631</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5015,17 +5015,17 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>klibbal</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Alnus glutinosa</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Alnus glutinosa</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>

--- a/artfynd/A 35468-2025 artfynd.xlsx
+++ b/artfynd/A 35468-2025 artfynd.xlsx
@@ -4166,7 +4166,7 @@
         <v>128877195</v>
       </c>
       <c r="B34" t="n">
-        <v>93014</v>
+        <v>93022</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4275,50 +4275,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128877167</v>
+        <v>128877203</v>
       </c>
       <c r="B35" t="n">
-        <v>8450</v>
+        <v>93022</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106545</v>
+        <v>2079</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>312765</v>
+        <v>312756</v>
       </c>
       <c r="R35" t="n">
-        <v>6523969</v>
+        <v>6524245</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4392,45 +4387,50 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128877203</v>
+        <v>128877167</v>
       </c>
       <c r="B36" t="n">
-        <v>93014</v>
+        <v>8450</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2079</v>
+        <v>106545</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>312756</v>
+        <v>312765</v>
       </c>
       <c r="R36" t="n">
-        <v>6524245</v>
+        <v>6523969</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4507,7 +4507,7 @@
         <v>128877166</v>
       </c>
       <c r="B37" t="n">
-        <v>90304</v>
+        <v>90308</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>128877168</v>
       </c>
       <c r="B38" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4717,10 +4717,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128877201</v>
+        <v>128877191</v>
       </c>
       <c r="B39" t="n">
-        <v>96941</v>
+        <v>80704</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4728,21 +4728,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2590</v>
+        <v>230185</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4752,10 +4752,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>312904</v>
+        <v>312882</v>
       </c>
       <c r="R39" t="n">
-        <v>6524032</v>
+        <v>6523636</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4798,6 +4798,21 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>klibbal</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -4814,10 +4829,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128877191</v>
+        <v>128877201</v>
       </c>
       <c r="B40" t="n">
-        <v>80700</v>
+        <v>96951</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4825,21 +4840,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>230185</v>
+        <v>2590</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4849,10 +4864,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>312882</v>
+        <v>312904</v>
       </c>
       <c r="R40" t="n">
-        <v>6523636</v>
+        <v>6524032</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4895,21 +4910,6 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>klibbal</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Alnus glutinosa</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Alnus glutinosa</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5046,7 +5046,7 @@
         <v>128877199</v>
       </c>
       <c r="B42" t="n">
-        <v>96941</v>
+        <v>96951</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         <v>128877196</v>
       </c>
       <c r="B43" t="n">
-        <v>93014</v>
+        <v>93022</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5255,7 +5255,7 @@
         <v>128877192</v>
       </c>
       <c r="B44" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5352,7 +5352,7 @@
         <v>128877194</v>
       </c>
       <c r="B45" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5449,7 +5449,7 @@
         <v>128877202</v>
       </c>
       <c r="B46" t="n">
-        <v>75155</v>
+        <v>75157</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
         <v>128877204</v>
       </c>
       <c r="B48" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 35468-2025 artfynd.xlsx
+++ b/artfynd/A 35468-2025 artfynd.xlsx
@@ -4275,45 +4275,50 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128877203</v>
+        <v>128877167</v>
       </c>
       <c r="B35" t="n">
-        <v>93022</v>
+        <v>8450</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2079</v>
+        <v>106545</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>312756</v>
+        <v>312765</v>
       </c>
       <c r="R35" t="n">
-        <v>6524245</v>
+        <v>6523969</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4387,50 +4392,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128877167</v>
+        <v>128877203</v>
       </c>
       <c r="B36" t="n">
-        <v>8450</v>
+        <v>93022</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106545</v>
+        <v>2079</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>312765</v>
+        <v>312756</v>
       </c>
       <c r="R36" t="n">
-        <v>6523969</v>
+        <v>6524245</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -5140,32 +5140,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128877196</v>
+        <v>128877192</v>
       </c>
       <c r="B43" t="n">
-        <v>93022</v>
+        <v>92826</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5175,10 +5175,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>312874</v>
+        <v>312952</v>
       </c>
       <c r="R43" t="n">
-        <v>6523945</v>
+        <v>6523854</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5221,21 +5221,6 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5252,7 +5237,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128877192</v>
+        <v>128877194</v>
       </c>
       <c r="B44" t="n">
         <v>92826</v>
@@ -5287,10 +5272,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>312952</v>
+        <v>312901</v>
       </c>
       <c r="R44" t="n">
-        <v>6523854</v>
+        <v>6523903</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5349,32 +5334,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128877194</v>
+        <v>128877196</v>
       </c>
       <c r="B45" t="n">
-        <v>92826</v>
+        <v>93022</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5384,10 +5369,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>312901</v>
+        <v>312874</v>
       </c>
       <c r="R45" t="n">
-        <v>6523903</v>
+        <v>6523945</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5430,6 +5415,21 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">

--- a/artfynd/A 35468-2025 artfynd.xlsx
+++ b/artfynd/A 35468-2025 artfynd.xlsx
@@ -4166,7 +4166,7 @@
         <v>128877195</v>
       </c>
       <c r="B34" t="n">
-        <v>93022</v>
+        <v>93029</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4275,50 +4275,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128877167</v>
+        <v>128877203</v>
       </c>
       <c r="B35" t="n">
-        <v>8450</v>
+        <v>93029</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106545</v>
+        <v>2079</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>312765</v>
+        <v>312756</v>
       </c>
       <c r="R35" t="n">
-        <v>6523969</v>
+        <v>6524245</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4392,45 +4387,50 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128877203</v>
+        <v>128877167</v>
       </c>
       <c r="B36" t="n">
-        <v>93022</v>
+        <v>8450</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2079</v>
+        <v>106545</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>312756</v>
+        <v>312765</v>
       </c>
       <c r="R36" t="n">
-        <v>6524245</v>
+        <v>6523969</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4507,7 +4507,7 @@
         <v>128877166</v>
       </c>
       <c r="B37" t="n">
-        <v>90308</v>
+        <v>90315</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4717,10 +4717,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128877191</v>
+        <v>128877172</v>
       </c>
       <c r="B39" t="n">
-        <v>80704</v>
+        <v>4779</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4728,34 +4728,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>230185</v>
+        <v>102306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>312882</v>
+        <v>312863</v>
       </c>
       <c r="R39" t="n">
-        <v>6523636</v>
+        <v>6523631</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4801,17 +4806,17 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>klibbal</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>Alnus glutinosa</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Alnus glutinosa</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -4832,7 +4837,7 @@
         <v>128877201</v>
       </c>
       <c r="B40" t="n">
-        <v>96951</v>
+        <v>96958</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4926,10 +4931,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128877172</v>
+        <v>128877191</v>
       </c>
       <c r="B41" t="n">
-        <v>4779</v>
+        <v>80704</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4937,39 +4942,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>102306</v>
+        <v>230185</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>312863</v>
+        <v>312882</v>
       </c>
       <c r="R41" t="n">
-        <v>6523631</v>
+        <v>6523636</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5015,17 +5015,17 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>klibbal</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Alnus glutinosa</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Alnus glutinosa</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5046,7 +5046,7 @@
         <v>128877199</v>
       </c>
       <c r="B42" t="n">
-        <v>96951</v>
+        <v>96958</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5140,32 +5140,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128877192</v>
+        <v>128877196</v>
       </c>
       <c r="B43" t="n">
-        <v>92826</v>
+        <v>93029</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5175,10 +5175,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>312952</v>
+        <v>312874</v>
       </c>
       <c r="R43" t="n">
-        <v>6523854</v>
+        <v>6523945</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5221,6 +5221,21 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5237,10 +5252,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128877194</v>
+        <v>128877192</v>
       </c>
       <c r="B44" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5272,10 +5287,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>312901</v>
+        <v>312952</v>
       </c>
       <c r="R44" t="n">
-        <v>6523903</v>
+        <v>6523854</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5334,32 +5349,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128877196</v>
+        <v>128877194</v>
       </c>
       <c r="B45" t="n">
-        <v>93022</v>
+        <v>92833</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5369,10 +5384,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>312874</v>
+        <v>312901</v>
       </c>
       <c r="R45" t="n">
-        <v>6523945</v>
+        <v>6523903</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5415,21 +5430,6 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5678,7 +5678,7 @@
         <v>128877204</v>
       </c>
       <c r="B48" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 35468-2025 artfynd.xlsx
+++ b/artfynd/A 35468-2025 artfynd.xlsx
@@ -4166,7 +4166,7 @@
         <v>128877195</v>
       </c>
       <c r="B34" t="n">
-        <v>93029</v>
+        <v>93031</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>128877203</v>
       </c>
       <c r="B35" t="n">
-        <v>93029</v>
+        <v>93031</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4507,7 +4507,7 @@
         <v>128877166</v>
       </c>
       <c r="B37" t="n">
-        <v>90315</v>
+        <v>90317</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>128877168</v>
       </c>
       <c r="B38" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4717,10 +4717,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128877172</v>
+        <v>128877201</v>
       </c>
       <c r="B39" t="n">
-        <v>4779</v>
+        <v>96960</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4728,39 +4728,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>102306</v>
+        <v>2590</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>312863</v>
+        <v>312904</v>
       </c>
       <c r="R39" t="n">
-        <v>6523631</v>
+        <v>6524032</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4803,21 +4798,6 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -4834,10 +4814,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128877201</v>
+        <v>128877172</v>
       </c>
       <c r="B40" t="n">
-        <v>96958</v>
+        <v>4779</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4845,34 +4825,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2590</v>
+        <v>102306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>312904</v>
+        <v>312863</v>
       </c>
       <c r="R40" t="n">
-        <v>6524032</v>
+        <v>6523631</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4915,6 +4900,21 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -4934,7 +4934,7 @@
         <v>128877191</v>
       </c>
       <c r="B41" t="n">
-        <v>80704</v>
+        <v>80706</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
         <v>128877199</v>
       </c>
       <c r="B42" t="n">
-        <v>96958</v>
+        <v>96960</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5140,32 +5140,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128877196</v>
+        <v>128877192</v>
       </c>
       <c r="B43" t="n">
-        <v>93029</v>
+        <v>92835</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5175,10 +5175,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>312874</v>
+        <v>312952</v>
       </c>
       <c r="R43" t="n">
-        <v>6523945</v>
+        <v>6523854</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5221,21 +5221,6 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5252,32 +5237,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128877192</v>
+        <v>128877196</v>
       </c>
       <c r="B44" t="n">
-        <v>92833</v>
+        <v>93031</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5287,10 +5272,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>312952</v>
+        <v>312874</v>
       </c>
       <c r="R44" t="n">
-        <v>6523854</v>
+        <v>6523945</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5333,6 +5318,21 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5352,7 +5352,7 @@
         <v>128877194</v>
       </c>
       <c r="B45" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5449,7 +5449,7 @@
         <v>128877202</v>
       </c>
       <c r="B46" t="n">
-        <v>75157</v>
+        <v>75159</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
         <v>128877204</v>
       </c>
       <c r="B48" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 35468-2025 artfynd.xlsx
+++ b/artfynd/A 35468-2025 artfynd.xlsx
@@ -4717,10 +4717,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128877201</v>
+        <v>128877191</v>
       </c>
       <c r="B39" t="n">
-        <v>96960</v>
+        <v>80706</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4728,21 +4728,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2590</v>
+        <v>230185</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4752,10 +4752,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>312904</v>
+        <v>312882</v>
       </c>
       <c r="R39" t="n">
-        <v>6524032</v>
+        <v>6523636</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4798,6 +4798,21 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>klibbal</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -4814,10 +4829,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128877172</v>
+        <v>128877201</v>
       </c>
       <c r="B40" t="n">
-        <v>4779</v>
+        <v>96960</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4825,39 +4840,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>102306</v>
+        <v>2590</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>312863</v>
+        <v>312904</v>
       </c>
       <c r="R40" t="n">
-        <v>6523631</v>
+        <v>6524032</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4900,21 +4910,6 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -4931,10 +4926,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128877191</v>
+        <v>128877172</v>
       </c>
       <c r="B41" t="n">
-        <v>80706</v>
+        <v>4779</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4942,34 +4937,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>230185</v>
+        <v>102306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>312882</v>
+        <v>312863</v>
       </c>
       <c r="R41" t="n">
-        <v>6523636</v>
+        <v>6523631</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5015,17 +5015,17 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>klibbal</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Alnus glutinosa</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Alnus glutinosa</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5140,7 +5140,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128877192</v>
+        <v>128877194</v>
       </c>
       <c r="B43" t="n">
         <v>92835</v>
@@ -5175,10 +5175,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>312952</v>
+        <v>312901</v>
       </c>
       <c r="R43" t="n">
-        <v>6523854</v>
+        <v>6523903</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5349,7 +5349,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128877194</v>
+        <v>128877192</v>
       </c>
       <c r="B45" t="n">
         <v>92835</v>
@@ -5384,10 +5384,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>312901</v>
+        <v>312952</v>
       </c>
       <c r="R45" t="n">
-        <v>6523903</v>
+        <v>6523854</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5675,10 +5675,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128877204</v>
+        <v>128877198</v>
       </c>
       <c r="B48" t="n">
-        <v>92835</v>
+        <v>8450</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5686,34 +5686,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>312745</v>
+        <v>312874</v>
       </c>
       <c r="R48" t="n">
-        <v>6524371</v>
+        <v>6523945</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5756,6 +5761,21 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -5772,10 +5792,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128877198</v>
+        <v>128877204</v>
       </c>
       <c r="B49" t="n">
-        <v>8450</v>
+        <v>92835</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5783,39 +5803,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>312874</v>
+        <v>312745</v>
       </c>
       <c r="R49" t="n">
-        <v>6523945</v>
+        <v>6524371</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5858,21 +5873,6 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">

--- a/artfynd/A 35468-2025 artfynd.xlsx
+++ b/artfynd/A 35468-2025 artfynd.xlsx
@@ -4166,7 +4166,7 @@
         <v>128877195</v>
       </c>
       <c r="B34" t="n">
-        <v>93031</v>
+        <v>91592</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>128877203</v>
       </c>
       <c r="B35" t="n">
-        <v>93031</v>
+        <v>91592</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4507,7 +4507,7 @@
         <v>128877166</v>
       </c>
       <c r="B37" t="n">
-        <v>90317</v>
+        <v>90318</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4717,10 +4717,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128877191</v>
+        <v>128877201</v>
       </c>
       <c r="B39" t="n">
-        <v>80706</v>
+        <v>96986</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4728,21 +4728,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>230185</v>
+        <v>2590</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4752,10 +4752,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>312882</v>
+        <v>312904</v>
       </c>
       <c r="R39" t="n">
-        <v>6523636</v>
+        <v>6524032</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4798,21 +4798,6 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>klibbal</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Alnus glutinosa</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Alnus glutinosa</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -4829,10 +4814,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128877201</v>
+        <v>128877191</v>
       </c>
       <c r="B40" t="n">
-        <v>96960</v>
+        <v>80706</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4840,21 +4825,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2590</v>
+        <v>230185</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4864,10 +4849,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>312904</v>
+        <v>312882</v>
       </c>
       <c r="R40" t="n">
-        <v>6524032</v>
+        <v>6523636</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4910,6 +4895,21 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>klibbal</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5046,7 +5046,7 @@
         <v>128877199</v>
       </c>
       <c r="B42" t="n">
-        <v>96960</v>
+        <v>96986</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5140,32 +5140,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128877194</v>
+        <v>128877196</v>
       </c>
       <c r="B43" t="n">
-        <v>92835</v>
+        <v>91592</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5175,10 +5175,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>312901</v>
+        <v>312874</v>
       </c>
       <c r="R43" t="n">
-        <v>6523903</v>
+        <v>6523945</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5221,6 +5221,21 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5237,32 +5252,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128877196</v>
+        <v>128877192</v>
       </c>
       <c r="B44" t="n">
-        <v>93031</v>
+        <v>92821</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5272,10 +5287,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>312874</v>
+        <v>312952</v>
       </c>
       <c r="R44" t="n">
-        <v>6523945</v>
+        <v>6523854</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5318,21 +5333,6 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5349,10 +5349,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128877192</v>
+        <v>128877194</v>
       </c>
       <c r="B45" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5384,10 +5384,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>312952</v>
+        <v>312901</v>
       </c>
       <c r="R45" t="n">
-        <v>6523854</v>
+        <v>6523903</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5446,10 +5446,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128877202</v>
+        <v>128877170</v>
       </c>
       <c r="B46" t="n">
-        <v>75159</v>
+        <v>5197</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5457,34 +5457,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6426</v>
+        <v>105930</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>312754</v>
+        <v>312863</v>
       </c>
       <c r="R46" t="n">
-        <v>6524211</v>
+        <v>6523631</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5558,10 +5563,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128877170</v>
+        <v>128877202</v>
       </c>
       <c r="B47" t="n">
-        <v>5197</v>
+        <v>75159</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5569,39 +5574,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>105930</v>
+        <v>6426</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>312863</v>
+        <v>312754</v>
       </c>
       <c r="R47" t="n">
-        <v>6523631</v>
+        <v>6524211</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5795,7 +5795,7 @@
         <v>128877204</v>
       </c>
       <c r="B49" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 35468-2025 artfynd.xlsx
+++ b/artfynd/A 35468-2025 artfynd.xlsx
@@ -4166,7 +4166,7 @@
         <v>128877195</v>
       </c>
       <c r="B34" t="n">
-        <v>91592</v>
+        <v>91593</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4275,45 +4275,50 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128877203</v>
+        <v>128877167</v>
       </c>
       <c r="B35" t="n">
-        <v>91592</v>
+        <v>8450</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2079</v>
+        <v>106545</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>312756</v>
+        <v>312765</v>
       </c>
       <c r="R35" t="n">
-        <v>6524245</v>
+        <v>6523969</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4387,50 +4392,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128877167</v>
+        <v>128877203</v>
       </c>
       <c r="B36" t="n">
-        <v>8450</v>
+        <v>91593</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106545</v>
+        <v>2079</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>312765</v>
+        <v>312756</v>
       </c>
       <c r="R36" t="n">
-        <v>6523969</v>
+        <v>6524245</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4717,10 +4717,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128877201</v>
+        <v>128877191</v>
       </c>
       <c r="B39" t="n">
-        <v>96986</v>
+        <v>80706</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4728,21 +4728,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2590</v>
+        <v>230185</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4752,10 +4752,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>312904</v>
+        <v>312882</v>
       </c>
       <c r="R39" t="n">
-        <v>6524032</v>
+        <v>6523636</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4798,6 +4798,21 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>klibbal</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -4814,10 +4829,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128877191</v>
+        <v>128877201</v>
       </c>
       <c r="B40" t="n">
-        <v>80706</v>
+        <v>96987</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4825,21 +4840,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>230185</v>
+        <v>2590</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4849,10 +4864,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>312882</v>
+        <v>312904</v>
       </c>
       <c r="R40" t="n">
-        <v>6523636</v>
+        <v>6524032</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4895,21 +4910,6 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>klibbal</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Alnus glutinosa</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Alnus glutinosa</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5046,7 +5046,7 @@
         <v>128877199</v>
       </c>
       <c r="B42" t="n">
-        <v>96986</v>
+        <v>96987</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5140,32 +5140,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128877196</v>
+        <v>128877192</v>
       </c>
       <c r="B43" t="n">
-        <v>91592</v>
+        <v>92822</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5175,10 +5175,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>312874</v>
+        <v>312952</v>
       </c>
       <c r="R43" t="n">
-        <v>6523945</v>
+        <v>6523854</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5221,21 +5221,6 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5252,10 +5237,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128877192</v>
+        <v>128877194</v>
       </c>
       <c r="B44" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5287,10 +5272,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>312952</v>
+        <v>312901</v>
       </c>
       <c r="R44" t="n">
-        <v>6523854</v>
+        <v>6523903</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5349,32 +5334,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128877194</v>
+        <v>128877196</v>
       </c>
       <c r="B45" t="n">
-        <v>92821</v>
+        <v>91593</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5384,10 +5369,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>312901</v>
+        <v>312874</v>
       </c>
       <c r="R45" t="n">
-        <v>6523903</v>
+        <v>6523945</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5430,6 +5415,21 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5446,10 +5446,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128877170</v>
+        <v>128877202</v>
       </c>
       <c r="B46" t="n">
-        <v>5197</v>
+        <v>75159</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5457,39 +5457,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>105930</v>
+        <v>6426</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>312863</v>
+        <v>312754</v>
       </c>
       <c r="R46" t="n">
-        <v>6523631</v>
+        <v>6524211</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5563,10 +5558,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128877202</v>
+        <v>128877170</v>
       </c>
       <c r="B47" t="n">
-        <v>75159</v>
+        <v>5197</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5574,34 +5569,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6426</v>
+        <v>105930</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>312754</v>
+        <v>312863</v>
       </c>
       <c r="R47" t="n">
-        <v>6524211</v>
+        <v>6523631</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5795,7 +5795,7 @@
         <v>128877204</v>
       </c>
       <c r="B49" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 35468-2025 artfynd.xlsx
+++ b/artfynd/A 35468-2025 artfynd.xlsx
@@ -4717,10 +4717,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128877191</v>
+        <v>128877201</v>
       </c>
       <c r="B39" t="n">
-        <v>80706</v>
+        <v>96988</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4728,21 +4728,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>230185</v>
+        <v>2590</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4752,10 +4752,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>312882</v>
+        <v>312904</v>
       </c>
       <c r="R39" t="n">
-        <v>6523636</v>
+        <v>6524032</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4798,21 +4798,6 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>klibbal</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Alnus glutinosa</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Alnus glutinosa</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -4829,10 +4814,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128877201</v>
+        <v>128877172</v>
       </c>
       <c r="B40" t="n">
-        <v>96987</v>
+        <v>4779</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4840,34 +4825,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2590</v>
+        <v>102306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>312904</v>
+        <v>312863</v>
       </c>
       <c r="R40" t="n">
-        <v>6524032</v>
+        <v>6523631</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4910,6 +4900,21 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -4926,10 +4931,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128877172</v>
+        <v>128877191</v>
       </c>
       <c r="B41" t="n">
-        <v>4779</v>
+        <v>80706</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4937,39 +4942,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>102306</v>
+        <v>230185</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>312863</v>
+        <v>312882</v>
       </c>
       <c r="R41" t="n">
-        <v>6523631</v>
+        <v>6523636</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5015,17 +5015,17 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>klibbal</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Alnus glutinosa</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Alnus glutinosa</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5046,7 +5046,7 @@
         <v>128877199</v>
       </c>
       <c r="B42" t="n">
-        <v>96987</v>
+        <v>96988</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5140,32 +5140,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128877192</v>
+        <v>128877196</v>
       </c>
       <c r="B43" t="n">
-        <v>92822</v>
+        <v>91593</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5175,10 +5175,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>312952</v>
+        <v>312874</v>
       </c>
       <c r="R43" t="n">
-        <v>6523854</v>
+        <v>6523945</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5221,6 +5221,21 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5237,7 +5252,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128877194</v>
+        <v>128877192</v>
       </c>
       <c r="B44" t="n">
         <v>92822</v>
@@ -5272,10 +5287,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>312901</v>
+        <v>312952</v>
       </c>
       <c r="R44" t="n">
-        <v>6523903</v>
+        <v>6523854</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5334,32 +5349,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128877196</v>
+        <v>128877194</v>
       </c>
       <c r="B45" t="n">
-        <v>91593</v>
+        <v>92822</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5369,10 +5384,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>312874</v>
+        <v>312901</v>
       </c>
       <c r="R45" t="n">
-        <v>6523945</v>
+        <v>6523903</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5415,21 +5430,6 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">

--- a/artfynd/A 35468-2025 artfynd.xlsx
+++ b/artfynd/A 35468-2025 artfynd.xlsx
@@ -4166,7 +4166,7 @@
         <v>128877195</v>
       </c>
       <c r="B34" t="n">
-        <v>91593</v>
+        <v>91596</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4275,50 +4275,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128877167</v>
+        <v>128877203</v>
       </c>
       <c r="B35" t="n">
-        <v>8450</v>
+        <v>91596</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106545</v>
+        <v>2079</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>312765</v>
+        <v>312756</v>
       </c>
       <c r="R35" t="n">
-        <v>6523969</v>
+        <v>6524245</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4392,45 +4387,50 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128877203</v>
+        <v>128877167</v>
       </c>
       <c r="B36" t="n">
-        <v>91593</v>
+        <v>8450</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2079</v>
+        <v>106545</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>312756</v>
+        <v>312765</v>
       </c>
       <c r="R36" t="n">
-        <v>6524245</v>
+        <v>6523969</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4507,7 +4507,7 @@
         <v>128877166</v>
       </c>
       <c r="B37" t="n">
-        <v>90318</v>
+        <v>90321</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>128877168</v>
       </c>
       <c r="B38" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>128877201</v>
       </c>
       <c r="B39" t="n">
-        <v>96988</v>
+        <v>96992</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4934,7 +4934,7 @@
         <v>128877191</v>
       </c>
       <c r="B41" t="n">
-        <v>80706</v>
+        <v>80708</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
         <v>128877199</v>
       </c>
       <c r="B42" t="n">
-        <v>96988</v>
+        <v>96992</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         <v>128877196</v>
       </c>
       <c r="B43" t="n">
-        <v>91593</v>
+        <v>91596</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5255,7 +5255,7 @@
         <v>128877192</v>
       </c>
       <c r="B44" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5352,7 +5352,7 @@
         <v>128877194</v>
       </c>
       <c r="B45" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5446,10 +5446,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128877202</v>
+        <v>128877170</v>
       </c>
       <c r="B46" t="n">
-        <v>75159</v>
+        <v>5197</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5457,34 +5457,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6426</v>
+        <v>105930</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>312754</v>
+        <v>312863</v>
       </c>
       <c r="R46" t="n">
-        <v>6524211</v>
+        <v>6523631</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5558,10 +5563,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128877170</v>
+        <v>128877202</v>
       </c>
       <c r="B47" t="n">
-        <v>5197</v>
+        <v>75161</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5569,39 +5574,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>105930</v>
+        <v>6426</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>312863</v>
+        <v>312754</v>
       </c>
       <c r="R47" t="n">
-        <v>6523631</v>
+        <v>6524211</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5795,7 +5795,7 @@
         <v>128877204</v>
       </c>
       <c r="B49" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 35468-2025 artfynd.xlsx
+++ b/artfynd/A 35468-2025 artfynd.xlsx
@@ -4275,45 +4275,50 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128877203</v>
+        <v>128877167</v>
       </c>
       <c r="B35" t="n">
-        <v>91596</v>
+        <v>8450</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2079</v>
+        <v>106545</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>312756</v>
+        <v>312765</v>
       </c>
       <c r="R35" t="n">
-        <v>6524245</v>
+        <v>6523969</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4387,50 +4392,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128877167</v>
+        <v>128877203</v>
       </c>
       <c r="B36" t="n">
-        <v>8450</v>
+        <v>91596</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106545</v>
+        <v>2079</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>312765</v>
+        <v>312756</v>
       </c>
       <c r="R36" t="n">
-        <v>6523969</v>
+        <v>6524245</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -5675,10 +5675,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128877198</v>
+        <v>128877204</v>
       </c>
       <c r="B48" t="n">
-        <v>8450</v>
+        <v>92825</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5686,39 +5686,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>312874</v>
+        <v>312745</v>
       </c>
       <c r="R48" t="n">
-        <v>6523945</v>
+        <v>6524371</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5761,21 +5756,6 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -5792,10 +5772,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128877204</v>
+        <v>128877198</v>
       </c>
       <c r="B49" t="n">
-        <v>92825</v>
+        <v>8450</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5803,34 +5783,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Keddebo, Boh</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>312745</v>
+        <v>312874</v>
       </c>
       <c r="R49" t="n">
-        <v>6524371</v>
+        <v>6523945</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5873,6 +5858,21 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
